--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52A7263-BD73-4902-840D-4B378CDA36EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B114059C-BF26-4F73-8B47-4726C15F7E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -2476,7 +2476,7 @@
         <v>46297</v>
       </c>
       <c r="E29" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>41</v>
@@ -2824,10 +2824,10 @@
         <v>19</v>
       </c>
       <c r="D42" s="10">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E42" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>41</v>
@@ -3517,7 +3517,9 @@
       <c r="D68" s="23">
         <v>46269</v>
       </c>
-      <c r="E68" s="7"/>
+      <c r="E68" s="7">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="F68" s="6" t="s">
         <v>59</v>
       </c>
@@ -3592,9 +3594,11 @@
         <v>46</v>
       </c>
       <c r="D71" s="23">
-        <v>46290</v>
-      </c>
-      <c r="E71" s="7"/>
+        <v>46291</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.5</v>
+      </c>
       <c r="F71" s="6" t="s">
         <v>176</v>
       </c>
@@ -3803,7 +3807,7 @@
         <v>46278</v>
       </c>
       <c r="E79" s="90">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="F79" s="88" t="s">
         <v>188</v>
@@ -4622,9 +4626,11 @@
         <v>51</v>
       </c>
       <c r="D111" s="29">
-        <v>46332</v>
-      </c>
-      <c r="E111" s="12"/>
+        <v>46333</v>
+      </c>
+      <c r="E111" s="12">
+        <v>0.5</v>
+      </c>
       <c r="F111" s="8" t="s">
         <v>42</v>
       </c>
@@ -5466,7 +5472,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="D2" s="94">
-        <f>IF(I2 = "KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2 = "U16",C2+"1:45",IF(I2 = "U15",C2+"1:30",IF(I2 = "U14",C2+"1:30",IF(I2 = "U13",C2+"1:35",IF(I2 = "U12_1",C2+"1:10",IF(I2 = "U12_2",C2+"1:10",IF(I2 = "U11",C2+"1:10",IF(I2 = "U10",C2+"1:03",C2+"3:00"))))))))))</f>
+        <f>IF(I2="KM",C2+"1:45",IF(I2="U23",C2+"1:45",IF(I2="U16",C2+"1:45",IF(I2="U15",C2+"1:30",IF(I2="U14",C2+"1:30",IF(I2="U13",C2+"1:35",IF(I2="U12_1",C2+"1:10",IF(I2="U12_2",C2+"1:10",IF(I2="U11",C2+"1:10",IF(I2="U10",C2+"1:03",IF(I2="U9",C2+"1:03",C2+"3:00")))))))))))</f>
         <v>0.72916666666666663</v>
       </c>
       <c r="E2" s="94" t="str">
@@ -5505,7 +5511,7 @@
         <v>0.75</v>
       </c>
       <c r="D3" s="94">
-        <f t="shared" ref="D3:D66" si="0">IF(I3 = "KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3 = "U16",C3+"1:45",IF(I3 = "U15",C3+"1:30",IF(I3 = "U14",C3+"1:30",IF(I3 = "U13",C3+"1:35",IF(I3 = "U12_1",C3+"1:10",IF(I3 = "U12_2",C3+"1:10",IF(I3 = "U11",C3+"1:10",IF(I3 = "U10",C3+"1:03",C3+"3:00"))))))))))</f>
+        <f t="shared" ref="D3:D66" si="0">IF(I3="KM",C3+"1:45",IF(I3="U23",C3+"1:45",IF(I3="U16",C3+"1:45",IF(I3="U15",C3+"1:30",IF(I3="U14",C3+"1:30",IF(I3="U13",C3+"1:35",IF(I3="U12_1",C3+"1:10",IF(I3="U12_2",C3+"1:10",IF(I3="U11",C3+"1:10",IF(I3="U10",C3+"1:03",IF(I3="U9",C3+"1:03",C3+"3:00")))))))))))</f>
         <v>0.82291666666666663</v>
       </c>
       <c r="E3" s="94" t="str">
@@ -6516,11 +6522,11 @@
       </c>
       <c r="C29" s="94">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D29" s="94">
         <f t="shared" si="0"/>
-        <v>0.86458333333333326</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E29" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
@@ -7019,15 +7025,15 @@
     <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="93">
         <f>'Nach Mannschaften sortiert'!D42</f>
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C42" s="94">
         <f>'Nach Mannschaften sortiert'!E42</f>
-        <v>0.70833333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D42" s="94">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E42" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
@@ -8001,7 +8007,7 @@
         <v>0.625</v>
       </c>
       <c r="D67" s="94">
-        <f t="shared" ref="D67:D130" si="1">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12_1",C67+"1:10",IF(I67 = "U12_2",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00"))))))))))</f>
+        <f t="shared" ref="D67:D130" si="1">IF(I67="KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67="U16",C67+"1:45",IF(I67="U15",C67+"1:30",IF(I67="U14",C67+"1:30",IF(I67="U13",C67+"1:35",IF(I67="U12_1",C67+"1:10",IF(I67="U12_2",C67+"1:10",IF(I67="U11",C67+"1:10",IF(I67="U10",C67+"1:03",IF(I67="U9",C67+"1:03",C67+"3:00")))))))))))</f>
         <v>0.6875</v>
       </c>
       <c r="E67" s="94" t="str">
@@ -8037,11 +8043,11 @@
       </c>
       <c r="C68" s="94">
         <f>'Nach Mannschaften sortiert'!E68</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D68" s="94">
         <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.75694444444444453</v>
       </c>
       <c r="E68" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
@@ -8150,15 +8156,15 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="93">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C71" s="94">
         <f>'Nach Mannschaften sortiert'!E71</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D71" s="94">
         <f t="shared" si="1"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="E71" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F71)</f>
@@ -8466,11 +8472,11 @@
       </c>
       <c r="C79" s="94">
         <f>'Nach Mannschaften sortiert'!E79</f>
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D79" s="94">
         <f t="shared" si="1"/>
-        <v>0.46527777777777779</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="E79" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F79)</f>
@@ -9367,7 +9373,7 @@
       </c>
       <c r="D102" s="94">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E102" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F102)</f>
@@ -9406,7 +9412,7 @@
       </c>
       <c r="D103" s="94">
         <f t="shared" si="1"/>
-        <v>0.58333333333333326</v>
+        <v>0.50208333333333333</v>
       </c>
       <c r="E103" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F103)</f>
@@ -9445,7 +9451,7 @@
       </c>
       <c r="D104" s="94">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E104" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F104)</f>
@@ -9484,7 +9490,7 @@
       </c>
       <c r="D105" s="94">
         <f t="shared" si="1"/>
-        <v>0.54166666666666674</v>
+        <v>0.4604166666666667</v>
       </c>
       <c r="E105" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F105)</f>
@@ -9523,7 +9529,7 @@
       </c>
       <c r="D106" s="94">
         <f t="shared" si="1"/>
-        <v>0.52083333333333326</v>
+        <v>0.43958333333333333</v>
       </c>
       <c r="E106" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F106)</f>
@@ -9562,7 +9568,7 @@
       </c>
       <c r="D107" s="94">
         <f t="shared" si="1"/>
-        <v>0.70833333333333337</v>
+        <v>0.62708333333333333</v>
       </c>
       <c r="E107" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F107)</f>
@@ -9601,7 +9607,7 @@
       </c>
       <c r="D108" s="94">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E108" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F108)</f>
@@ -9640,7 +9646,7 @@
       </c>
       <c r="D109" s="94">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>4.3750000000000004E-2</v>
       </c>
       <c r="E109" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F109)</f>
@@ -9679,7 +9685,7 @@
       </c>
       <c r="D110" s="94">
         <f t="shared" si="1"/>
-        <v>0.5625</v>
+        <v>0.48125000000000001</v>
       </c>
       <c r="E110" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F110)</f>
@@ -9710,15 +9716,15 @@
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="93">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C111" s="94">
         <f>'Nach Mannschaften sortiert'!E111</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D111" s="94">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.54374999999999996</v>
       </c>
       <c r="E111" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F111)</f>
@@ -10497,7 +10503,7 @@
         <v>0.375</v>
       </c>
       <c r="D131" s="94">
-        <f t="shared" ref="D131:D141" si="2">IF(I131 = "KM",C131+"1:45",IF(I131="U23",C131+"1:45",IF(I131 = "U16",C131+"1:45",IF(I131 = "U15",C131+"1:30",IF(I131 = "U14",C131+"1:30",IF(I131 = "U13",C131+"1:35",IF(I131 = "U12_1",C131+"1:10",IF(I131 = "U12_2",C131+"1:10",IF(I131 = "U11",C131+"1:10",IF(I131 = "U10",C131+"1:03",C131+"3:00"))))))))))</f>
+        <f t="shared" ref="D131:D141" si="2">IF(I131="KM",C131+"1:45",IF(I131="U23",C131+"1:45",IF(I131="U16",C131+"1:45",IF(I131="U15",C131+"1:30",IF(I131="U14",C131+"1:30",IF(I131="U13",C131+"1:35",IF(I131="U12_1",C131+"1:10",IF(I131="U12_2",C131+"1:10",IF(I131="U11",C131+"1:10",IF(I131="U10",C131+"1:03",IF(I131="U9",C131+"1:03",C131+"3:00")))))))))))</f>
         <v>0.5</v>
       </c>
       <c r="E131" s="94" t="str">
@@ -12116,7 +12122,7 @@
       </c>
       <c r="C27" s="104">
         <f>'ICS2'!C29</f>
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D27" s="57" t="str">
         <f>'ICS2'!E29</f>
@@ -12531,7 +12537,7 @@
       </c>
       <c r="C36" s="119">
         <f>'ICS2'!C68</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D36" s="117" t="str">
         <f>'ICS2'!E68</f>
@@ -13543,11 +13549,11 @@
       </c>
       <c r="B58" s="103">
         <f>'ICS2'!B71</f>
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C58" s="104">
         <f>'ICS2'!C71</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D58" s="57" t="str">
         <f>'ICS2'!E71</f>
@@ -13915,7 +13921,7 @@
       </c>
       <c r="C66" s="104">
         <f>'ICS2'!C79</f>
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="D66" s="57" t="str">
         <f>'ICS2'!E79</f>
@@ -16104,11 +16110,11 @@
       </c>
       <c r="B114" s="103">
         <f>'ICS2'!B42</f>
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="C114" s="104">
         <f>'ICS2'!C42</f>
-        <v>0.70833333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D114" s="57" t="str">
         <f>'ICS2'!E42</f>
@@ -17222,11 +17228,11 @@
       </c>
       <c r="B139" s="114">
         <f>'ICS2'!B111</f>
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C139" s="115">
         <f>'ICS2'!C111</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D139" s="113" t="str">
         <f>'ICS2'!E111</f>
@@ -18324,7 +18330,7 @@
       </c>
       <c r="E7" s="95">
         <f>'Nach Mannschaften sortiert'!E68</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F7" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F68</f>
@@ -19748,11 +19754,11 @@
       </c>
       <c r="D49" s="55">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E49" s="95">
         <f>'Nach Mannschaften sortiert'!E71</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F49" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F71</f>
@@ -19854,7 +19860,7 @@
       </c>
       <c r="E52" s="97">
         <f>'Nach Mannschaften sortiert'!E29</f>
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F52" s="48" t="str">
         <f>'Nach Mannschaften sortiert'!F29</f>
@@ -20426,11 +20432,11 @@
       </c>
       <c r="D69" s="55">
         <f>'Nach Mannschaften sortiert'!D111</f>
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="E69" s="95">
         <f>'Nach Mannschaften sortiert'!E111</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F69" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F111</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667EBCD0-F2C7-4604-80B0-19E9C76A14D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3857CC93-4392-4982-9845-69B3B94AA708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -2075,7 +2075,7 @@
         <v>46245</v>
       </c>
       <c r="E14" s="91">
-        <v>0.77083333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>194</v>
@@ -5971,11 +5971,11 @@
       </c>
       <c r="C14" s="94">
         <f>'Nach Mannschaften sortiert'!E14</f>
-        <v>0.77083333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D14" s="94">
         <f t="shared" ref="D14" si="1">IF(I14="KM",C14+"1:45",IF(I14="U23",C14+"1:45",IF(I14="U16",C14+"1:45",IF(I14="U15",C14+"1:30",IF(I14="U14",C14+"1:30",IF(I14="U13",C14+"1:35",IF(I14="U12_1",C14+"1:10",IF(I14="U12_2",C14+"1:10",IF(I14="U11",C14+"1:10",IF(I14="U10",C14+"1:03",IF(I14="U9",C14+"1:03",C14+"3:00")))))))))))</f>
-        <v>0.84375</v>
+        <v>0.86458333333333326</v>
       </c>
       <c r="E14" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3857CC93-4392-4982-9845-69B3B94AA708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF3527A-779D-4256-878A-AE6CE9D97554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="196">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -582,9 +582,6 @@
     <t>St.Georgen</t>
   </si>
   <si>
-    <t>XXX</t>
-  </si>
-  <si>
     <t>Spielfrei</t>
   </si>
   <si>
@@ -631,6 +628,12 @@
   </si>
   <si>
     <t>Wr. Neustadt</t>
+  </si>
+  <si>
+    <t>009:00</t>
+  </si>
+  <si>
+    <t>XXXXX</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2081,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>21</v>
@@ -3022,7 +3025,7 @@
       <c r="E49" s="22"/>
       <c r="F49" s="21"/>
       <c r="G49" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H49" s="21"/>
     </row>
@@ -3072,7 +3075,7 @@
         <v>9</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H51" s="21" t="s">
         <v>11</v>
@@ -3092,7 +3095,9 @@
       <c r="D52" s="28">
         <v>46292</v>
       </c>
-      <c r="E52" s="22"/>
+      <c r="E52" s="22">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="F52" s="21" t="s">
         <v>28</v>
       </c>
@@ -3124,7 +3129,7 @@
         <v>23</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H53" s="21" t="s">
         <v>11</v>
@@ -3175,7 +3180,7 @@
         <v>0.75</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G55" s="21" t="s">
         <v>165</v>
@@ -3201,7 +3206,7 @@
       <c r="E56" s="22"/>
       <c r="F56" s="21"/>
       <c r="G56" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H56" s="21"/>
     </row>
@@ -3226,7 +3231,7 @@
         <v>23</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H57" s="21" t="s">
         <v>11</v>
@@ -3248,10 +3253,10 @@
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H58" s="21" t="s">
         <v>15</v>
@@ -3296,10 +3301,10 @@
         <v>27</v>
       </c>
       <c r="D60" s="14">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="E60" s="15">
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="F60" s="13" t="s">
         <v>28</v>
@@ -3324,10 +3329,10 @@
         <v>27</v>
       </c>
       <c r="D61" s="14">
-        <v>46278</v>
+        <v>46288</v>
       </c>
       <c r="E61" s="15">
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>14</v>
@@ -3355,7 +3360,7 @@
         <v>46284</v>
       </c>
       <c r="E62" s="15">
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F62" s="13" t="s">
         <v>23</v>
@@ -3383,7 +3388,7 @@
         <v>46292</v>
       </c>
       <c r="E63" s="15">
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>28</v>
@@ -3408,10 +3413,10 @@
         <v>27</v>
       </c>
       <c r="D64" s="14">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E64" s="15">
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>167</v>
@@ -3439,7 +3444,7 @@
         <v>46306</v>
       </c>
       <c r="E65" s="15">
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>28</v>
@@ -3557,7 +3562,7 @@
         <v>59</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>11</v>
@@ -3579,10 +3584,10 @@
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>15</v>
@@ -3636,7 +3641,7 @@
         <v>176</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>15</v>
@@ -3663,7 +3668,7 @@
         <v>59</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>11</v>
@@ -3685,10 +3690,10 @@
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>15</v>
@@ -3715,7 +3720,7 @@
         <v>23</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>11</v>
@@ -3767,7 +3772,7 @@
         <v>23</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>11</v>
@@ -3787,12 +3792,14 @@
       <c r="D78" s="23">
         <v>46332</v>
       </c>
-      <c r="E78" s="7"/>
+      <c r="E78" s="7">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="F78" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>15</v>
@@ -3819,7 +3826,7 @@
         <v>59</v>
       </c>
       <c r="G79" s="88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H79" s="88" t="s">
         <v>11</v>
@@ -3843,7 +3850,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="F80" s="88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G80" s="88" t="s">
         <v>165</v>
@@ -3864,9 +3871,11 @@
         <v>47</v>
       </c>
       <c r="D81" s="89">
-        <v>46283</v>
-      </c>
-      <c r="E81" s="90"/>
+        <v>46284</v>
+      </c>
+      <c r="E81" s="90">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="F81" s="88" t="s">
         <v>28</v>
       </c>
@@ -3898,7 +3907,7 @@
         <v>23</v>
       </c>
       <c r="G82" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H82" s="88" t="s">
         <v>11</v>
@@ -3945,10 +3954,10 @@
       </c>
       <c r="E84" s="90"/>
       <c r="F84" s="88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G84" s="88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H84" s="88" t="s">
         <v>15</v>
@@ -4024,10 +4033,10 @@
       </c>
       <c r="E87" s="90"/>
       <c r="F87" s="88" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G87" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H87" s="88" t="s">
         <v>15</v>
@@ -4101,7 +4110,9 @@
       <c r="D90" s="24">
         <v>46276</v>
       </c>
-      <c r="E90" s="20"/>
+      <c r="E90" s="20">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="F90" s="19" t="s">
         <v>42</v>
       </c>
@@ -4124,14 +4135,16 @@
         <v>48</v>
       </c>
       <c r="D91" s="24">
-        <v>46283</v>
-      </c>
-      <c r="E91" s="20"/>
+        <v>46284</v>
+      </c>
+      <c r="E91" s="20">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="F91" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H91" s="19" t="s">
         <v>15</v>
@@ -4158,7 +4171,7 @@
         <v>23</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H92" s="19" t="s">
         <v>11</v>
@@ -4255,9 +4268,11 @@
         <v>48</v>
       </c>
       <c r="D96" s="24">
-        <v>46318</v>
-      </c>
-      <c r="E96" s="20"/>
+        <v>46320</v>
+      </c>
+      <c r="E96" s="20">
+        <v>0.5</v>
+      </c>
       <c r="F96" s="19" t="s">
         <v>42</v>
       </c>
@@ -4280,14 +4295,16 @@
         <v>48</v>
       </c>
       <c r="D97" s="24">
-        <v>46325</v>
-      </c>
-      <c r="E97" s="20"/>
+        <v>46326</v>
+      </c>
+      <c r="E97" s="20">
+        <v>0.4375</v>
+      </c>
       <c r="F97" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H97" s="19" t="s">
         <v>15</v>
@@ -4359,7 +4376,9 @@
       <c r="D100" s="86">
         <v>46305</v>
       </c>
-      <c r="E100" s="87"/>
+      <c r="E100" s="87" t="s">
+        <v>194</v>
+      </c>
       <c r="F100" s="85" t="s">
         <v>175</v>
       </c>
@@ -4381,10 +4400,12 @@
       <c r="C101" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="D101" s="86" t="s">
-        <v>178</v>
-      </c>
-      <c r="E101" s="87"/>
+      <c r="D101" s="86">
+        <v>46270</v>
+      </c>
+      <c r="E101" s="87">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="F101" s="85" t="s">
         <v>176</v>
       </c>
@@ -4406,10 +4427,12 @@
       <c r="C102" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="D102" s="86" t="s">
-        <v>178</v>
-      </c>
-      <c r="E102" s="87"/>
+      <c r="D102" s="86">
+        <v>46292</v>
+      </c>
+      <c r="E102" s="87">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="F102" s="85" t="s">
         <v>177</v>
       </c>
@@ -4432,9 +4455,11 @@
         <v>51</v>
       </c>
       <c r="D103" s="29">
-        <v>46269</v>
-      </c>
-      <c r="E103" s="12"/>
+        <v>46275</v>
+      </c>
+      <c r="E103" s="12">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="F103" s="8" t="s">
         <v>28</v>
       </c>
@@ -4489,7 +4514,7 @@
       <c r="E105" s="12"/>
       <c r="F105" s="8"/>
       <c r="G105" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H105" s="8"/>
     </row>
@@ -4511,10 +4536,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H106" s="8" t="s">
         <v>15</v>
@@ -4586,9 +4611,11 @@
         <v>51</v>
       </c>
       <c r="D109" s="29">
-        <v>46311</v>
-      </c>
-      <c r="E109" s="12"/>
+        <v>46312</v>
+      </c>
+      <c r="E109" s="12">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="F109" s="8" t="s">
         <v>59</v>
       </c>
@@ -4616,7 +4643,7 @@
       <c r="E110" s="12"/>
       <c r="F110" s="8"/>
       <c r="G110" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H110" s="8"/>
     </row>
@@ -4641,7 +4668,7 @@
         <v>23</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H111" s="8" t="s">
         <v>11</v>
@@ -4740,7 +4767,9 @@
       <c r="D115" s="26">
         <v>46291</v>
       </c>
-      <c r="E115" s="27"/>
+      <c r="E115" s="27">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="F115" s="25" t="s">
         <v>174</v>
       </c>
@@ -4762,8 +4791,8 @@
       <c r="C116" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D116" s="26">
-        <v>46091</v>
+      <c r="D116" s="26" t="s">
+        <v>195</v>
       </c>
       <c r="E116" s="27"/>
       <c r="F116" s="25" t="s">
@@ -4787,8 +4816,8 @@
       <c r="C117" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D117" s="26">
-        <v>46092</v>
+      <c r="D117" s="26" t="s">
+        <v>195</v>
       </c>
       <c r="E117" s="27"/>
       <c r="F117" s="25" t="s">
@@ -7360,7 +7389,7 @@
         <v>U16</v>
       </c>
       <c r="J49" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K49" t="s">
         <v>80</v>
@@ -7454,11 +7483,11 @@
       </c>
       <c r="C52" s="94">
         <f>'Nach Mannschaften sortiert'!E52</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D52" s="94">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.78125</v>
       </c>
       <c r="E52" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
@@ -7633,7 +7662,7 @@
         <v>U16</v>
       </c>
       <c r="J56" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K56" t="s">
         <v>80</v>
@@ -7762,15 +7791,15 @@
     <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="93">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="C60" s="94">
         <f>'Nach Mannschaften sortiert'!E60</f>
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="D60" s="94">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.5</v>
       </c>
       <c r="E60" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
@@ -7801,15 +7830,15 @@
     <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="93">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46278</v>
+        <v>46288</v>
       </c>
       <c r="C61" s="94">
         <f>'Nach Mannschaften sortiert'!E61</f>
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D61" s="94">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="E61" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
@@ -7844,11 +7873,11 @@
       </c>
       <c r="C62" s="94">
         <f>'Nach Mannschaften sortiert'!E62</f>
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D62" s="94">
         <f t="shared" si="0"/>
-        <v>0.58333333333333337</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="E62" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
@@ -7883,11 +7912,11 @@
       </c>
       <c r="C63" s="94">
         <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D63" s="94">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E63" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
@@ -7918,15 +7947,15 @@
     <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="93">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="C64" s="94">
         <f>'Nach Mannschaften sortiert'!E64</f>
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D64" s="94">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="E64" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F64)</f>
@@ -7961,11 +7990,11 @@
       </c>
       <c r="C65" s="94">
         <f>'Nach Mannschaften sortiert'!E65</f>
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D65" s="94">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.52083333333333326</v>
       </c>
       <c r="E65" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F65)</f>
@@ -8468,11 +8497,11 @@
       </c>
       <c r="C78" s="94">
         <f>'Nach Mannschaften sortiert'!E78</f>
-        <v>0</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D78" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E78" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F78)</f>
@@ -8581,15 +8610,15 @@
     <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81" s="93">
         <f>'Nach Mannschaften sortiert'!D81</f>
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C81" s="94">
         <f>'Nach Mannschaften sortiert'!E81</f>
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D81" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.50694444444444442</v>
       </c>
       <c r="E81" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F81)</f>
@@ -8936,11 +8965,11 @@
       </c>
       <c r="C90" s="94">
         <f>'Nach Mannschaften sortiert'!E90</f>
-        <v>0</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D90" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.81944444444444453</v>
       </c>
       <c r="E90" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F90)</f>
@@ -8971,15 +9000,15 @@
     <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91" s="93">
         <f>'Nach Mannschaften sortiert'!D91</f>
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C91" s="94">
         <f>'Nach Mannschaften sortiert'!E91</f>
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D91" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.46527777777777779</v>
       </c>
       <c r="E91" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F91)</f>
@@ -9166,15 +9195,15 @@
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="93">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="C96" s="94">
         <f>'Nach Mannschaften sortiert'!E96</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D96" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.54861111111111116</v>
       </c>
       <c r="E96" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F96)</f>
@@ -9205,15 +9234,15 @@
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="93">
         <f>'Nach Mannschaften sortiert'!D97</f>
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C97" s="94">
         <f>'Nach Mannschaften sortiert'!E97</f>
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="D97" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="E97" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F97)</f>
@@ -9324,13 +9353,13 @@
         <f>'Nach Mannschaften sortiert'!D100</f>
         <v>46305</v>
       </c>
-      <c r="C100" s="94">
+      <c r="C100" s="94" t="str">
         <f>'Nach Mannschaften sortiert'!E100</f>
-        <v>0</v>
-      </c>
-      <c r="D100" s="94">
+        <v>009:00</v>
+      </c>
+      <c r="D100" s="94" t="e">
         <f t="shared" si="2"/>
-        <v>4.3750000000000004E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E100" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F100)</f>
@@ -9359,17 +9388,17 @@
       </c>
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B101" s="93" t="str">
+      <c r="B101" s="93">
         <f>'Nach Mannschaften sortiert'!D101</f>
-        <v>XXX</v>
+        <v>46270</v>
       </c>
       <c r="C101" s="94">
         <f>'Nach Mannschaften sortiert'!E101</f>
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D101" s="94">
         <f t="shared" si="2"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.58541666666666659</v>
       </c>
       <c r="E101" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F101)</f>
@@ -9398,17 +9427,17 @@
       </c>
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B102" s="93" t="str">
+      <c r="B102" s="93">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>XXX</v>
+        <v>46292</v>
       </c>
       <c r="C102" s="94">
         <f>'Nach Mannschaften sortiert'!E102</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D102" s="94">
         <f t="shared" si="2"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.62708333333333333</v>
       </c>
       <c r="E102" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F102)</f>
@@ -9439,15 +9468,15 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="93">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="C103" s="94">
         <f>'Nach Mannschaften sortiert'!E103</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D103" s="94">
         <f t="shared" si="2"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.75208333333333333</v>
       </c>
       <c r="E103" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F103)</f>
@@ -9544,7 +9573,7 @@
         <v>U9</v>
       </c>
       <c r="J105" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K105" t="s">
         <v>80</v>
@@ -9673,15 +9702,15 @@
     <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109" s="93">
         <f>'Nach Mannschaften sortiert'!D109</f>
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C109" s="94">
         <f>'Nach Mannschaften sortiert'!E109</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D109" s="94">
         <f t="shared" si="2"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.43958333333333333</v>
       </c>
       <c r="E109" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F109)</f>
@@ -9739,7 +9768,7 @@
         <v>U9</v>
       </c>
       <c r="J110" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K110" t="s">
         <v>80</v>
@@ -9911,11 +9940,11 @@
       </c>
       <c r="C115" s="94">
         <f>'Nach Mannschaften sortiert'!E115</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D115" s="94">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>0.52083333333333326</v>
       </c>
       <c r="E115" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F115)</f>
@@ -9944,9 +9973,9 @@
       </c>
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B116" s="93">
+      <c r="B116" s="93" t="str">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46091</v>
+        <v>XXXXX</v>
       </c>
       <c r="C116" s="94">
         <f>'Nach Mannschaften sortiert'!E116</f>
@@ -9983,9 +10012,9 @@
       </c>
     </row>
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B117" s="93">
+      <c r="B117" s="93" t="str">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46092</v>
+        <v>XXXXX</v>
       </c>
       <c r="C117" s="94">
         <f>'Nach Mannschaften sortiert'!E117</f>
@@ -10051,7 +10080,7 @@
         <v>U7</v>
       </c>
       <c r="J118" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K118" t="s">
         <v>80</v>
@@ -10090,7 +10119,7 @@
         <v>U7</v>
       </c>
       <c r="J119" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K119" t="s">
         <v>80</v>
@@ -10129,7 +10158,7 @@
         <v>U7</v>
       </c>
       <c r="J120" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K120" t="s">
         <v>80</v>
@@ -10168,7 +10197,7 @@
         <v>U7</v>
       </c>
       <c r="J121" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K121" t="s">
         <v>80</v>
@@ -10207,7 +10236,7 @@
         <v>U7</v>
       </c>
       <c r="J122" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K122" t="s">
         <v>80</v>
@@ -11062,9 +11091,9 @@
         <f>'ICS2'!I117</f>
         <v>U8</v>
       </c>
-      <c r="B2" s="103">
+      <c r="B2" s="103" t="str">
         <f>'ICS2'!B117</f>
-        <v>46092</v>
+        <v>XXXXX</v>
       </c>
       <c r="C2" s="104">
         <f>'ICS2'!C117</f>
@@ -12653,11 +12682,11 @@
       </c>
       <c r="B37" s="110">
         <f>'ICS2'!B103</f>
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="C37" s="111">
         <f>'ICS2'!C103</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D37" s="109" t="str">
         <f>'ICS2'!E103</f>
@@ -12791,11 +12820,11 @@
       </c>
       <c r="B40" s="118">
         <f>'ICS2'!B60</f>
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="C40" s="119">
         <f>'ICS2'!C60</f>
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="D40" s="117" t="str">
         <f>'ICS2'!E60</f>
@@ -12886,9 +12915,9 @@
         <f>'ICS2'!B100</f>
         <v>46305</v>
       </c>
-      <c r="C42" s="104">
+      <c r="C42" s="104" t="str">
         <f>'ICS2'!C100</f>
-        <v>0</v>
+        <v>009:00</v>
       </c>
       <c r="D42" s="57" t="str">
         <f>'ICS2'!E100</f>
@@ -12931,11 +12960,11 @@
       </c>
       <c r="B43" s="103">
         <f>'ICS2'!B60</f>
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="C43" s="104">
         <f>'ICS2'!C60</f>
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="D43" s="57" t="str">
         <f>'ICS2'!E60</f>
@@ -12975,13 +13004,13 @@
         <f>'ICS2'!I101</f>
         <v>U10</v>
       </c>
-      <c r="B44" s="103" t="str">
+      <c r="B44" s="103">
         <f>'ICS2'!B101</f>
-        <v>XXX</v>
+        <v>46270</v>
       </c>
       <c r="C44" s="104">
         <f>'ICS2'!C101</f>
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D44" s="57" t="str">
         <f>'ICS2'!E101</f>
@@ -13022,13 +13051,13 @@
         <f>'ICS2'!I102</f>
         <v>U10</v>
       </c>
-      <c r="B45" s="103" t="str">
+      <c r="B45" s="103">
         <f>'ICS2'!B102</f>
-        <v>XXX</v>
+        <v>46292</v>
       </c>
       <c r="C45" s="104">
         <f>'ICS2'!C102</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D45" s="57" t="str">
         <f>'ICS2'!E102</f>
@@ -13121,7 +13150,7 @@
       </c>
       <c r="C47" s="107">
         <f>'ICS2'!C90</f>
-        <v>0</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D47" s="105" t="str">
         <f>'ICS2'!E90</f>
@@ -13163,11 +13192,11 @@
       </c>
       <c r="B48" s="103">
         <f>'ICS2'!B91</f>
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C48" s="104">
         <f>'ICS2'!C91</f>
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D48" s="57" t="str">
         <f>'ICS2'!E91</f>
@@ -13347,11 +13376,11 @@
       </c>
       <c r="B52" s="118">
         <f>'ICS2'!B81</f>
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C52" s="119">
         <f>'ICS2'!C81</f>
-        <v>0</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D52" s="117" t="str">
         <f>'ICS2'!E81</f>
@@ -13393,11 +13422,11 @@
       </c>
       <c r="B53" s="106">
         <f>'ICS2'!B96</f>
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="C53" s="107">
         <f>'ICS2'!C96</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D53" s="105" t="str">
         <f>'ICS2'!E96</f>
@@ -13439,11 +13468,11 @@
       </c>
       <c r="B54" s="114">
         <f>'ICS2'!B97</f>
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C54" s="115">
         <f>'ICS2'!C97</f>
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="D54" s="113" t="str">
         <f>'ICS2'!E97</f>
@@ -13673,7 +13702,7 @@
       </c>
       <c r="C59" s="122">
         <f>'ICS2'!C62</f>
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D59" s="120" t="str">
         <f>'ICS2'!E62</f>
@@ -13765,7 +13794,7 @@
       </c>
       <c r="C61" s="104">
         <f>'ICS2'!C62</f>
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D61" s="57" t="str">
         <f>'ICS2'!E62</f>
@@ -13903,7 +13932,7 @@
       </c>
       <c r="C64" s="104">
         <f>'ICS2'!C78</f>
-        <v>0</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D64" s="57" t="str">
         <f>'ICS2'!E78</f>
@@ -14220,7 +14249,7 @@
       </c>
       <c r="C71" s="119">
         <f>'ICS2'!C52</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D71" s="117" t="str">
         <f>'ICS2'!E52</f>
@@ -14404,7 +14433,7 @@
       </c>
       <c r="C75" s="119">
         <f>'ICS2'!C63</f>
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D75" s="117" t="str">
         <f>'ICS2'!E63</f>
@@ -14676,11 +14705,11 @@
       </c>
       <c r="B81" s="103">
         <f>'ICS2'!B61</f>
-        <v>46278</v>
+        <v>46288</v>
       </c>
       <c r="C81" s="104">
         <f>'ICS2'!C61</f>
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D81" s="57" t="str">
         <f>'ICS2'!E61</f>
@@ -14814,11 +14843,11 @@
       </c>
       <c r="B84" s="103">
         <f>'ICS2'!B64</f>
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="C84" s="104">
         <f>'ICS2'!C64</f>
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="D84" s="57" t="str">
         <f>'ICS2'!E64</f>
@@ -15048,7 +15077,7 @@
       </c>
       <c r="C89" s="119">
         <f>'ICS2'!C65</f>
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D89" s="117" t="str">
         <f>'ICS2'!E65</f>
@@ -15090,11 +15119,11 @@
       </c>
       <c r="B90" s="110">
         <f>'ICS2'!B109</f>
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C90" s="111">
         <f>'ICS2'!C109</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D90" s="109" t="str">
         <f>'ICS2'!E109</f>
@@ -15735,11 +15764,11 @@
       </c>
       <c r="B104" s="103">
         <f>'ICS2'!B61</f>
-        <v>46278</v>
+        <v>46288</v>
       </c>
       <c r="C104" s="104">
         <f>'ICS2'!C61</f>
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D104" s="57" t="str">
         <f>'ICS2'!E61</f>
@@ -16684,9 +16713,9 @@
         <f>'ICS2'!I116</f>
         <v>U8</v>
       </c>
-      <c r="B125" s="103">
+      <c r="B125" s="103" t="str">
         <f>'ICS2'!B116</f>
-        <v>46091</v>
+        <v>XXXXX</v>
       </c>
       <c r="C125" s="104">
         <f>'ICS2'!C116</f>
@@ -16823,7 +16852,7 @@
       </c>
       <c r="C128" s="104">
         <f>'ICS2'!C115</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D128" s="57" t="str">
         <f>'ICS2'!E115</f>
@@ -18332,11 +18361,11 @@
       </c>
       <c r="D5" s="55">
         <f>'Nach Mannschaften sortiert'!D60</f>
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="E5" s="95">
         <f>'Nach Mannschaften sortiert'!E60</f>
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="F5" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F60</f>
@@ -18978,11 +19007,11 @@
       </c>
       <c r="D24" s="51">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="E24" s="99">
         <f>'Nach Mannschaften sortiert'!E103</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F24" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!F103</f>
@@ -19356,7 +19385,7 @@
       </c>
       <c r="E35" s="99">
         <f>'Nach Mannschaften sortiert'!E90</f>
-        <v>0</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="F35" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!F90</f>
@@ -19386,11 +19415,11 @@
       </c>
       <c r="D36" s="55">
         <f>'Nach Mannschaften sortiert'!D61</f>
-        <v>46278</v>
+        <v>46288</v>
       </c>
       <c r="E36" s="95">
         <f>'Nach Mannschaften sortiert'!E61</f>
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F36" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F61</f>
@@ -19424,7 +19453,7 @@
       </c>
       <c r="E37" s="95">
         <f>'Nach Mannschaften sortiert'!E62</f>
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F37" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F62</f>
@@ -19522,11 +19551,11 @@
       </c>
       <c r="D40" s="55">
         <f>'Nach Mannschaften sortiert'!D64</f>
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E40" s="95">
         <f>'Nach Mannschaften sortiert'!E64</f>
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F40" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F64</f>
@@ -19696,7 +19725,7 @@
       </c>
       <c r="E45" s="99">
         <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F45" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!F63</f>
@@ -19798,7 +19827,7 @@
       </c>
       <c r="E48" s="97">
         <f>'Nach Mannschaften sortiert'!E52</f>
-        <v>0</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F48" s="48" t="str">
         <f>'Nach Mannschaften sortiert'!F52</f>
@@ -20236,11 +20265,11 @@
       </c>
       <c r="D61" s="55">
         <f>'Nach Mannschaften sortiert'!D96</f>
-        <v>46318</v>
+        <v>46320</v>
       </c>
       <c r="E61" s="95">
         <f>'Nach Mannschaften sortiert'!E96</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F61" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F96</f>
@@ -20612,7 +20641,7 @@
       </c>
       <c r="E72" s="95">
         <f>'Nach Mannschaften sortiert'!E115</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F72" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F115</f>
@@ -20640,9 +20669,9 @@
         <f>'Nach Mannschaften sortiert'!C116</f>
         <v>U8</v>
       </c>
-      <c r="D73" s="55">
+      <c r="D73" s="55" t="str">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>46091</v>
+        <v>XXXXX</v>
       </c>
       <c r="E73" s="95">
         <f>'Nach Mannschaften sortiert'!E116</f>
@@ -20674,9 +20703,9 @@
         <f>'Nach Mannschaften sortiert'!C117</f>
         <v>U8</v>
       </c>
-      <c r="D74" s="55">
+      <c r="D74" s="55" t="str">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>46092</v>
+        <v>XXXXX</v>
       </c>
       <c r="E74" s="95">
         <f>'Nach Mannschaften sortiert'!E117</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF3527A-779D-4256-878A-AE6CE9D97554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ED685A-C5B7-4986-BACC-E236505C1DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="194">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -628,12 +628,6 @@
   </si>
   <si>
     <t>Wr. Neustadt</t>
-  </si>
-  <si>
-    <t>009:00</t>
-  </si>
-  <si>
-    <t>XXXXX</t>
   </si>
 </sst>
 </file>
@@ -3041,9 +3035,11 @@
         <v>12</v>
       </c>
       <c r="D50" s="28">
-        <v>46278</v>
-      </c>
-      <c r="E50" s="22"/>
+        <v>46277</v>
+      </c>
+      <c r="E50" s="22">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="F50" s="21" t="s">
         <v>43</v>
       </c>
@@ -3249,11 +3245,13 @@
         <v>12</v>
       </c>
       <c r="D58" s="28">
-        <v>46334</v>
-      </c>
-      <c r="E58" s="22"/>
+        <v>46333</v>
+      </c>
+      <c r="E58" s="22">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="F58" s="21" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G58" s="21" t="s">
         <v>179</v>
@@ -3363,7 +3361,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>166</v>
@@ -3447,7 +3445,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>170</v>
@@ -3472,7 +3470,7 @@
         <v>46313</v>
       </c>
       <c r="E66" s="15">
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F66" s="13" t="s">
         <v>171</v>
@@ -3528,7 +3526,7 @@
         <v>46327</v>
       </c>
       <c r="E68" s="15">
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>43</v>
@@ -3580,9 +3578,11 @@
         <v>46</v>
       </c>
       <c r="D70" s="23">
-        <v>46276</v>
-      </c>
-      <c r="E70" s="7"/>
+        <v>46277</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="F70" s="6" t="s">
         <v>182</v>
       </c>
@@ -3738,9 +3738,11 @@
         <v>46</v>
       </c>
       <c r="D76" s="23">
-        <v>46318</v>
-      </c>
-      <c r="E76" s="7"/>
+        <v>46319</v>
+      </c>
+      <c r="E76" s="7">
+        <v>0.625</v>
+      </c>
       <c r="F76" s="6" t="s">
         <v>174</v>
       </c>
@@ -4029,9 +4031,11 @@
         <v>47</v>
       </c>
       <c r="D87" s="89">
-        <v>46325</v>
-      </c>
-      <c r="E87" s="90"/>
+        <v>46327</v>
+      </c>
+      <c r="E87" s="90">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="F87" s="88" t="s">
         <v>189</v>
       </c>
@@ -4216,9 +4220,11 @@
         <v>48</v>
       </c>
       <c r="D94" s="24">
-        <v>46304</v>
-      </c>
-      <c r="E94" s="20"/>
+        <v>46305</v>
+      </c>
+      <c r="E94" s="20">
+        <v>0.5625</v>
+      </c>
       <c r="F94" s="19" t="s">
         <v>174</v>
       </c>
@@ -4351,7 +4357,9 @@
       <c r="D99" s="86">
         <v>46277</v>
       </c>
-      <c r="E99" s="87"/>
+      <c r="E99" s="87">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="F99" s="85" t="s">
         <v>41</v>
       </c>
@@ -4376,8 +4384,8 @@
       <c r="D100" s="86">
         <v>46305</v>
       </c>
-      <c r="E100" s="87" t="s">
-        <v>194</v>
+      <c r="E100" s="87">
+        <v>0.375</v>
       </c>
       <c r="F100" s="85" t="s">
         <v>175</v>
@@ -4428,7 +4436,7 @@
         <v>49</v>
       </c>
       <c r="D102" s="86">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="E102" s="87">
         <v>0.58333333333333337</v>
@@ -4455,7 +4463,7 @@
         <v>51</v>
       </c>
       <c r="D103" s="29">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="E103" s="12">
         <v>0.70833333333333337</v>
@@ -4742,7 +4750,9 @@
       <c r="D114" s="26">
         <v>46284</v>
       </c>
-      <c r="E114" s="27"/>
+      <c r="E114" s="27">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="F114" s="25" t="s">
         <v>9</v>
       </c>
@@ -4791,10 +4801,12 @@
       <c r="C116" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D116" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="E116" s="27"/>
+      <c r="D116" s="26">
+        <v>46305</v>
+      </c>
+      <c r="E116" s="27">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="F116" s="25" t="s">
         <v>42</v>
       </c>
@@ -4816,8 +4828,8 @@
       <c r="C117" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D117" s="26" t="s">
-        <v>195</v>
+      <c r="D117" s="26">
+        <v>46278</v>
       </c>
       <c r="E117" s="27"/>
       <c r="F117" s="25" t="s">
@@ -6141,7 +6153,7 @@
         <v>U16</v>
       </c>
       <c r="J17" s="82" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="K17" t="s">
         <v>78</v>
@@ -7401,15 +7413,15 @@
     <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="93">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="C50" s="94">
         <f>'Nach Mannschaften sortiert'!E50</f>
-        <v>0</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D50" s="94">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.59375</v>
       </c>
       <c r="E50" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
@@ -7713,19 +7725,19 @@
     <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="93">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="C58" s="94">
         <f>'Nach Mannschaften sortiert'!E58</f>
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D58" s="94">
         <f t="shared" si="0"/>
-        <v>7.2916666666666671E-2</v>
+        <v>0.61458333333333326</v>
       </c>
       <c r="E58" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
-        <v>EISENSTADT</v>
+        <v>TRAUSDORF</v>
       </c>
       <c r="G58" t="str">
         <f>'Nach Mannschaften sortiert'!H58</f>
@@ -7881,7 +7893,7 @@
       </c>
       <c r="E62" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
-        <v>NEUFELD</v>
+        <v>GROßHÖFLEIN</v>
       </c>
       <c r="G62" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
@@ -7998,7 +8010,7 @@
       </c>
       <c r="E65" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F65)</f>
-        <v>GROßHÖFLEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G65" t="str">
         <f>'Nach Mannschaften sortiert'!H65</f>
@@ -8029,11 +8041,11 @@
       </c>
       <c r="C66" s="94">
         <f>'Nach Mannschaften sortiert'!E66</f>
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D66" s="94">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.52083333333333326</v>
       </c>
       <c r="E66" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F66)</f>
@@ -8107,11 +8119,11 @@
       </c>
       <c r="C68" s="94">
         <f>'Nach Mannschaften sortiert'!E68</f>
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D68" s="94">
         <f t="shared" ref="D68:D131" si="2">IF(I68="KM",C68+"1:45",IF(I68="U23",C68+"1:45",IF(I68="U16",C68+"1:45",IF(I68="U15",C68+"1:30",IF(I68="U14",C68+"1:30",IF(I68="U13",C68+"1:35",IF(I68="U12_1",C68+"1:10",IF(I68="U12_2",C68+"1:10",IF(I68="U11",C68+"1:10",IF(I68="U10",C68+"1:03",IF(I68="U9",C68+"1:03",C68+"3:00")))))))))))</f>
-        <v>0.6875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E68" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
@@ -8181,15 +8193,15 @@
     <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70" s="93">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C70" s="94">
         <f>'Nach Mannschaften sortiert'!E70</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D70" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="E70" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F70)</f>
@@ -8415,15 +8427,15 @@
     <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76" s="93">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C76" s="94">
         <f>'Nach Mannschaften sortiert'!E76</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D76" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="E76" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F76)</f>
@@ -8844,15 +8856,15 @@
     <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87" s="93">
         <f>'Nach Mannschaften sortiert'!D87</f>
-        <v>46325</v>
+        <v>46327</v>
       </c>
       <c r="C87" s="94">
         <f>'Nach Mannschaften sortiert'!E87</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D87" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="E87" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F87)</f>
@@ -9117,15 +9129,15 @@
     <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="93">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C94" s="94">
         <f>'Nach Mannschaften sortiert'!E94</f>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="D94" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="E94" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F94)</f>
@@ -9316,11 +9328,11 @@
       </c>
       <c r="C99" s="94">
         <f>'Nach Mannschaften sortiert'!E99</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D99" s="94">
         <f t="shared" si="2"/>
-        <v>4.3750000000000004E-2</v>
+        <v>0.5229166666666667</v>
       </c>
       <c r="E99" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F99)</f>
@@ -9353,13 +9365,13 @@
         <f>'Nach Mannschaften sortiert'!D100</f>
         <v>46305</v>
       </c>
-      <c r="C100" s="94" t="str">
+      <c r="C100" s="94">
         <f>'Nach Mannschaften sortiert'!E100</f>
-        <v>009:00</v>
-      </c>
-      <c r="D100" s="94" t="e">
+        <v>0.375</v>
+      </c>
+      <c r="D100" s="94">
         <f t="shared" si="2"/>
-        <v>#VALUE!</v>
+        <v>0.41875000000000001</v>
       </c>
       <c r="E100" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F100)</f>
@@ -9429,7 +9441,7 @@
     <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102" s="93">
         <f>'Nach Mannschaften sortiert'!D102</f>
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="C102" s="94">
         <f>'Nach Mannschaften sortiert'!E102</f>
@@ -9468,7 +9480,7 @@
     <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103" s="93">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="C103" s="94">
         <f>'Nach Mannschaften sortiert'!E103</f>
@@ -9901,11 +9913,11 @@
       </c>
       <c r="C114" s="94">
         <f>'Nach Mannschaften sortiert'!E114</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D114" s="94">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>0.52083333333333326</v>
       </c>
       <c r="E114" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F114)</f>
@@ -9973,17 +9985,17 @@
       </c>
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B116" s="93" t="str">
+      <c r="B116" s="93">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>XXXXX</v>
+        <v>46305</v>
       </c>
       <c r="C116" s="94">
         <f>'Nach Mannschaften sortiert'!E116</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D116" s="94">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>0.52083333333333326</v>
       </c>
       <c r="E116" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F116)</f>
@@ -10012,9 +10024,9 @@
       </c>
     </row>
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B117" s="93" t="str">
+      <c r="B117" s="93">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>XXXXX</v>
+        <v>46278</v>
       </c>
       <c r="C117" s="94">
         <f>'Nach Mannschaften sortiert'!E117</f>
@@ -11091,9 +11103,9 @@
         <f>'ICS2'!I117</f>
         <v>U8</v>
       </c>
-      <c r="B2" s="103" t="str">
+      <c r="B2" s="103">
         <f>'ICS2'!B117</f>
-        <v>XXXXX</v>
+        <v>46278</v>
       </c>
       <c r="C2" s="104">
         <f>'ICS2'!C117</f>
@@ -12682,7 +12694,7 @@
       </c>
       <c r="B37" s="110">
         <f>'ICS2'!B103</f>
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="C37" s="111">
         <f>'ICS2'!C103</f>
@@ -12870,7 +12882,7 @@
       </c>
       <c r="C41" s="111">
         <f>'ICS2'!C99</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D41" s="109" t="str">
         <f>'ICS2'!E99</f>
@@ -12915,9 +12927,9 @@
         <f>'ICS2'!B100</f>
         <v>46305</v>
       </c>
-      <c r="C42" s="104" t="str">
+      <c r="C42" s="104">
         <f>'ICS2'!C100</f>
-        <v>009:00</v>
+        <v>0.375</v>
       </c>
       <c r="D42" s="57" t="str">
         <f>'ICS2'!E100</f>
@@ -13053,7 +13065,7 @@
       </c>
       <c r="B45" s="103">
         <f>'ICS2'!B102</f>
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="C45" s="104">
         <f>'ICS2'!C102</f>
@@ -13330,11 +13342,11 @@
       </c>
       <c r="B51" s="103">
         <f>'ICS2'!B94</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C51" s="104">
         <f>'ICS2'!C94</f>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="D51" s="57" t="str">
         <f>'ICS2'!E94</f>
@@ -13518,7 +13530,7 @@
       </c>
       <c r="C55" s="119">
         <f>'ICS2'!C114</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D55" s="117" t="str">
         <f>'ICS2'!E114</f>
@@ -13560,11 +13572,11 @@
       </c>
       <c r="B56" s="103">
         <f>'ICS2'!B70</f>
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C56" s="104">
         <f>'ICS2'!C70</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D56" s="57" t="str">
         <f>'ICS2'!E70</f>
@@ -13706,7 +13718,7 @@
       </c>
       <c r="D59" s="120" t="str">
         <f>'ICS2'!E62</f>
-        <v>NEUFELD</v>
+        <v>GROßHÖFLEIN</v>
       </c>
       <c r="E59" s="120" t="str">
         <f>'ICS2'!H62</f>
@@ -13798,7 +13810,7 @@
       </c>
       <c r="D61" s="57" t="str">
         <f>'ICS2'!E62</f>
-        <v>NEUFELD</v>
+        <v>GROßHÖFLEIN</v>
       </c>
       <c r="E61" s="57" t="str">
         <f>'ICS2'!H62</f>
@@ -13836,11 +13848,11 @@
       </c>
       <c r="B62" s="103">
         <f>'ICS2'!B76</f>
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C62" s="104">
         <f>'ICS2'!C76</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="D62" s="57" t="str">
         <f>'ICS2'!E76</f>
@@ -14337,11 +14349,11 @@
       </c>
       <c r="B73" s="103">
         <f>'ICS2'!B87</f>
-        <v>46325</v>
+        <v>46327</v>
       </c>
       <c r="C73" s="104">
         <f>'ICS2'!C87</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D73" s="57" t="str">
         <f>'ICS2'!E87</f>
@@ -14939,7 +14951,7 @@
       </c>
       <c r="C86" s="104">
         <f>'ICS2'!C66</f>
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D86" s="57" t="str">
         <f>'ICS2'!E66</f>
@@ -15031,7 +15043,7 @@
       </c>
       <c r="C88" s="104">
         <f>'ICS2'!C68</f>
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="D88" s="57" t="str">
         <f>'ICS2'!E68</f>
@@ -15081,7 +15093,7 @@
       </c>
       <c r="D89" s="117" t="str">
         <f>'ICS2'!E65</f>
-        <v>GROßHÖFLEIN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="E89" s="117" t="str">
         <f>'ICS2'!H65</f>
@@ -15442,11 +15454,11 @@
       </c>
       <c r="B97" s="103">
         <f>'ICS2'!B50</f>
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="C97" s="104">
         <f>'ICS2'!C50</f>
-        <v>0</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="D97" s="57" t="str">
         <f>'ICS2'!E50</f>
@@ -16713,13 +16725,13 @@
         <f>'ICS2'!I116</f>
         <v>U8</v>
       </c>
-      <c r="B125" s="103" t="str">
+      <c r="B125" s="103">
         <f>'ICS2'!B116</f>
-        <v>XXXXX</v>
+        <v>46305</v>
       </c>
       <c r="C125" s="104">
         <f>'ICS2'!C116</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D125" s="57" t="str">
         <f>'ICS2'!E116</f>
@@ -17498,15 +17510,15 @@
       </c>
       <c r="B143" s="125">
         <f>'Nach Mannschaften sortiert'!D58</f>
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="C143" s="126">
         <f>'Nach Mannschaften sortiert'!E58</f>
-        <v>0</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="D143" s="124" t="str">
         <f>'Nach Mannschaften sortiert'!F58</f>
-        <v>Eisenstadt</v>
+        <v>Trausdorf</v>
       </c>
       <c r="E143" s="124" t="str">
         <f>'Nach Mannschaften sortiert'!G58</f>
@@ -18735,11 +18747,11 @@
       </c>
       <c r="D16" s="49">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="E16" s="97">
         <f>'Nach Mannschaften sortiert'!E50</f>
-        <v>0</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="F16" s="48" t="str">
         <f>'Nach Mannschaften sortiert'!F50</f>
@@ -19007,7 +19019,7 @@
       </c>
       <c r="D24" s="51">
         <f>'Nach Mannschaften sortiert'!D103</f>
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="E24" s="99">
         <f>'Nach Mannschaften sortiert'!E103</f>
@@ -19457,7 +19469,7 @@
       </c>
       <c r="F37" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F62</f>
-        <v>Neufeld</v>
+        <v>Großhöflein</v>
       </c>
       <c r="G37" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!G62</f>
@@ -19619,11 +19631,11 @@
       </c>
       <c r="D42" s="55">
         <f>'Nach Mannschaften sortiert'!D94</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E42" s="95">
         <f>'Nach Mannschaften sortiert'!E94</f>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="F42" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F94</f>
@@ -19789,11 +19801,11 @@
       </c>
       <c r="D47" s="55">
         <f>'Nach Mannschaften sortiert'!D70</f>
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E47" s="95">
         <f>'Nach Mannschaften sortiert'!E70</f>
-        <v>0</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="F47" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F70</f>
@@ -20303,7 +20315,7 @@
       </c>
       <c r="E62" s="98">
         <f>'Nach Mannschaften sortiert'!E68</f>
-        <v>0.625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F62" s="46" t="str">
         <f>'Nach Mannschaften sortiert'!F68</f>
@@ -20607,7 +20619,7 @@
       </c>
       <c r="E71" s="95">
         <f>'Nach Mannschaften sortiert'!E114</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F71" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F114</f>
@@ -20669,13 +20681,13 @@
         <f>'Nach Mannschaften sortiert'!C116</f>
         <v>U8</v>
       </c>
-      <c r="D73" s="55" t="str">
+      <c r="D73" s="55">
         <f>'Nach Mannschaften sortiert'!D116</f>
-        <v>XXXXX</v>
+        <v>46305</v>
       </c>
       <c r="E73" s="95">
         <f>'Nach Mannschaften sortiert'!E116</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F73" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F116</f>
@@ -20703,9 +20715,9 @@
         <f>'Nach Mannschaften sortiert'!C117</f>
         <v>U8</v>
       </c>
-      <c r="D74" s="55" t="str">
+      <c r="D74" s="55">
         <f>'Nach Mannschaften sortiert'!D117</f>
-        <v>XXXXX</v>
+        <v>46278</v>
       </c>
       <c r="E74" s="95">
         <f>'Nach Mannschaften sortiert'!E117</f>
@@ -20909,11 +20921,11 @@
       </c>
       <c r="D80" s="49">
         <f>'Nach Mannschaften sortiert'!D76</f>
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E80" s="97">
         <f>'Nach Mannschaften sortiert'!E76</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="F80" s="48" t="str">
         <f>'Nach Mannschaften sortiert'!F76</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ED685A-C5B7-4986-BACC-E236505C1DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A318C5CC-D65B-454C-BBA4-2969CFCA2AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="197">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -628,6 +628,15 @@
   </si>
   <si>
     <t>Wr. Neustadt</t>
+  </si>
+  <si>
+    <t>bittere 1:0 Niederlage, somit aus dem BFV-Cup ausgeschieden</t>
+  </si>
+  <si>
+    <t>nach einer 2:0 Führung noch 4:2 verloren</t>
+  </si>
+  <si>
+    <t>9:2 für Kittsee</t>
   </si>
 </sst>
 </file>
@@ -5826,6 +5835,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
         <v>KITTSEE</v>
       </c>
+      <c r="F9" s="82" t="s">
+        <v>194</v>
+      </c>
       <c r="G9" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
         <v>Auswärts</v>
@@ -6374,6 +6386,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
         <v>KITTSEE</v>
       </c>
+      <c r="F23" s="82" t="s">
+        <v>195</v>
+      </c>
       <c r="G23" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Auswärts</v>
@@ -6880,6 +6895,9 @@
       <c r="E36" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
         <v>KITTSEE</v>
+      </c>
+      <c r="F36" s="82" t="s">
+        <v>196</v>
       </c>
       <c r="G36" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A318C5CC-D65B-454C-BBA4-2969CFCA2AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F32BD1-50F5-4352-9359-D1AE5D3A7BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -3532,10 +3532,10 @@
         <v>27</v>
       </c>
       <c r="D68" s="14">
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="E68" s="15">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>43</v>
@@ -3961,9 +3961,11 @@
         <v>47</v>
       </c>
       <c r="D84" s="89">
-        <v>46304</v>
-      </c>
-      <c r="E84" s="90"/>
+        <v>46305</v>
+      </c>
+      <c r="E84" s="90">
+        <v>0.6875</v>
+      </c>
       <c r="F84" s="88" t="s">
         <v>186</v>
       </c>
@@ -4840,7 +4842,9 @@
       <c r="D117" s="26">
         <v>46278</v>
       </c>
-      <c r="E117" s="27"/>
+      <c r="E117" s="27">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="F117" s="25" t="s">
         <v>59</v>
       </c>
@@ -8133,15 +8137,15 @@
     <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68" s="93">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="C68" s="94">
         <f>'Nach Mannschaften sortiert'!E68</f>
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D68" s="94">
         <f t="shared" ref="D68:D131" si="2">IF(I68="KM",C68+"1:45",IF(I68="U23",C68+"1:45",IF(I68="U16",C68+"1:45",IF(I68="U15",C68+"1:30",IF(I68="U14",C68+"1:30",IF(I68="U13",C68+"1:35",IF(I68="U12_1",C68+"1:10",IF(I68="U12_2",C68+"1:10",IF(I68="U11",C68+"1:10",IF(I68="U10",C68+"1:03",IF(I68="U9",C68+"1:03",C68+"3:00")))))))))))</f>
-        <v>0.66666666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E68" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
@@ -8757,15 +8761,15 @@
     <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84" s="93">
         <f>'Nach Mannschaften sortiert'!D84</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C84" s="94">
         <f>'Nach Mannschaften sortiert'!E84</f>
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="D84" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.73611111111111116</v>
       </c>
       <c r="E84" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
@@ -10048,11 +10052,11 @@
       </c>
       <c r="C117" s="94">
         <f>'Nach Mannschaften sortiert'!E117</f>
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D117" s="94">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>0.54166666666666674</v>
       </c>
       <c r="E117" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F117)</f>
@@ -11127,7 +11131,7 @@
       </c>
       <c r="C2" s="104">
         <f>'ICS2'!C117</f>
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D2" s="57" t="str">
         <f>'ICS2'!E117</f>
@@ -14229,11 +14233,11 @@
       </c>
       <c r="B70" s="103">
         <f>'ICS2'!B84</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C70" s="104">
         <f>'ICS2'!C84</f>
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="D70" s="57" t="str">
         <f>'ICS2'!E84</f>
@@ -15057,11 +15061,11 @@
       </c>
       <c r="B88" s="103">
         <f>'ICS2'!B68</f>
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="C88" s="104">
         <f>'ICS2'!C68</f>
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D88" s="57" t="str">
         <f>'ICS2'!E68</f>
@@ -20329,11 +20333,11 @@
       </c>
       <c r="D62" s="47">
         <f>'Nach Mannschaften sortiert'!D68</f>
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="E62" s="98">
         <f>'Nach Mannschaften sortiert'!E68</f>
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F62" s="46" t="str">
         <f>'Nach Mannschaften sortiert'!F68</f>
@@ -20739,7 +20743,7 @@
       </c>
       <c r="E74" s="95">
         <f>'Nach Mannschaften sortiert'!E117</f>
-        <v>0</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F74" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F117</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F32BD1-50F5-4352-9359-D1AE5D3A7BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB7723E-EC8B-497D-92A0-241BC6C2A5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="201">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -637,6 +637,18 @@
   </si>
   <si>
     <t>9:2 für Kittsee</t>
+  </si>
+  <si>
+    <t>4:0 für Deutsch-Jahndorf</t>
+  </si>
+  <si>
+    <t>3:0 für Deutsch-Jahndof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:2 </t>
+  </si>
+  <si>
+    <t>2:4 für Tadten</t>
   </si>
 </sst>
 </file>
@@ -3395,7 +3407,7 @@
         <v>46292</v>
       </c>
       <c r="E63" s="15">
-        <v>0.60416666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>28</v>
@@ -3614,10 +3626,10 @@
         <v>46</v>
       </c>
       <c r="D71" s="23">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="E71" s="7">
-        <v>0.4375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>23</v>
@@ -3697,7 +3709,9 @@
       <c r="D74" s="23">
         <v>46304</v>
       </c>
-      <c r="E74" s="7"/>
+      <c r="E74" s="7">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F74" s="6" t="s">
         <v>181</v>
       </c>
@@ -3801,10 +3815,10 @@
         <v>46</v>
       </c>
       <c r="D78" s="23">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="E78" s="7">
-        <v>0.72916666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>42</v>
@@ -3938,7 +3952,9 @@
       <c r="D83" s="89">
         <v>46297</v>
       </c>
-      <c r="E83" s="90"/>
+      <c r="E83" s="90">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="F83" s="88" t="s">
         <v>163</v>
       </c>
@@ -3964,7 +3980,7 @@
         <v>46305</v>
       </c>
       <c r="E84" s="90">
-        <v>0.6875</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="F84" s="88" t="s">
         <v>186</v>
@@ -6432,6 +6448,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
+      <c r="F24" s="82" t="s">
+        <v>197</v>
+      </c>
       <c r="G24" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
         <v>Auswärts</v>
@@ -6471,6 +6490,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F25" s="82" t="s">
+        <v>199</v>
+      </c>
       <c r="G25" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Heim</v>
@@ -6942,6 +6964,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
+      <c r="F37" s="82" t="s">
+        <v>198</v>
+      </c>
       <c r="G37" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
         <v>Auswärts</v>
@@ -6981,6 +7006,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F38" s="82" t="s">
+        <v>200</v>
+      </c>
       <c r="G38" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
         <v>Heim</v>
@@ -7946,11 +7974,11 @@
       </c>
       <c r="C63" s="94">
         <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0.60416666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="D63" s="94">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E63" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
@@ -8254,15 +8282,15 @@
     <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71" s="93">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="C71" s="94">
         <f>'Nach Mannschaften sortiert'!E71</f>
-        <v>0.4375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D71" s="94">
         <f t="shared" si="2"/>
-        <v>0.4861111111111111</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E71" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F71)</f>
@@ -8375,11 +8403,11 @@
       </c>
       <c r="C74" s="94">
         <f>'Nach Mannschaften sortiert'!E74</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D74" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.71527777777777779</v>
       </c>
       <c r="E74" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F74)</f>
@@ -8527,15 +8555,15 @@
     <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78" s="93">
         <f>'Nach Mannschaften sortiert'!D78</f>
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C78" s="94">
         <f>'Nach Mannschaften sortiert'!E78</f>
-        <v>0.72916666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D78" s="94">
         <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="E78" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F78)</f>
@@ -8726,11 +8754,11 @@
       </c>
       <c r="C83" s="94">
         <f>'Nach Mannschaften sortiert'!E83</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D83" s="94">
         <f t="shared" si="2"/>
-        <v>4.8611111111111112E-2</v>
+        <v>0.71527777777777779</v>
       </c>
       <c r="E83" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
@@ -8765,11 +8793,11 @@
       </c>
       <c r="C84" s="94">
         <f>'Nach Mannschaften sortiert'!E84</f>
-        <v>0.6875</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D84" s="94">
         <f t="shared" si="2"/>
-        <v>0.73611111111111116</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="E84" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
@@ -13640,11 +13668,11 @@
       </c>
       <c r="B57" s="121">
         <f>'ICS2'!B71</f>
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="C57" s="122">
         <f>'ICS2'!C71</f>
-        <v>0.4375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D57" s="120" t="str">
         <f>'ICS2'!E71</f>
@@ -13782,7 +13810,7 @@
       </c>
       <c r="C60" s="104">
         <f>'ICS2'!C74</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D60" s="57" t="str">
         <f>'ICS2'!E74</f>
@@ -13962,11 +13990,11 @@
       </c>
       <c r="B64" s="103">
         <f>'ICS2'!B78</f>
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C64" s="104">
         <f>'ICS2'!C78</f>
-        <v>0.72916666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="D64" s="57" t="str">
         <f>'ICS2'!E78</f>
@@ -14191,7 +14219,7 @@
       </c>
       <c r="C69" s="107">
         <f>'ICS2'!C83</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D69" s="105" t="str">
         <f>'ICS2'!E83</f>
@@ -14237,7 +14265,7 @@
       </c>
       <c r="C70" s="104">
         <f>'ICS2'!C84</f>
-        <v>0.6875</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="D70" s="57" t="str">
         <f>'ICS2'!E84</f>
@@ -14467,7 +14495,7 @@
       </c>
       <c r="C75" s="119">
         <f>'ICS2'!C63</f>
-        <v>0.60416666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="D75" s="117" t="str">
         <f>'ICS2'!E63</f>
@@ -19721,11 +19749,11 @@
       </c>
       <c r="D44" s="51">
         <f>'Nach Mannschaften sortiert'!D71</f>
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="E44" s="99">
         <f>'Nach Mannschaften sortiert'!E71</f>
-        <v>0.4375</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F44" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!F71</f>
@@ -19759,7 +19787,7 @@
       </c>
       <c r="E45" s="99">
         <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0.60416666666666663</v>
+        <v>0.4375</v>
       </c>
       <c r="F45" s="50" t="str">
         <f>'Nach Mannschaften sortiert'!F63</f>
@@ -20607,7 +20635,7 @@
       </c>
       <c r="E70" s="97">
         <f>'Nach Mannschaften sortiert'!E74</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F70" s="48" t="str">
         <f>'Nach Mannschaften sortiert'!F74</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB7723E-EC8B-497D-92A0-241BC6C2A5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ACC682-A0AC-4FA5-A72E-C8176F6687A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="207">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -649,6 +649,24 @@
   </si>
   <si>
     <t>2:4 für Tadten</t>
+  </si>
+  <si>
+    <t>5:1 für Mönchhof</t>
+  </si>
+  <si>
+    <t>2:0 für Mönchhof</t>
+  </si>
+  <si>
+    <t>16:1 für Leithaprodersdorf</t>
+  </si>
+  <si>
+    <t>4:2 für St. Georgen/Eisenstadt</t>
+  </si>
+  <si>
+    <t>5:1 für SPG ASV</t>
+  </si>
+  <si>
+    <t>4:3 für Stotzing</t>
   </si>
 </sst>
 </file>
@@ -6532,6 +6550,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
         <v>MÖNCHHOF</v>
       </c>
+      <c r="F26" s="82" t="s">
+        <v>201</v>
+      </c>
       <c r="G26" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
         <v>Auswärts</v>
@@ -7048,6 +7069,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
         <v>MÖNCHHOF</v>
       </c>
+      <c r="F39" s="82" t="s">
+        <v>202</v>
+      </c>
       <c r="G39" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
         <v>Auswärts</v>
@@ -7867,6 +7891,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F60" s="82" t="s">
+        <v>204</v>
+      </c>
       <c r="G60" t="str">
         <f>'Nach Mannschaften sortiert'!H60</f>
         <v>Heim</v>
@@ -8218,6 +8245,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F69)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F69" s="82" t="s">
+        <v>206</v>
+      </c>
       <c r="G69" t="str">
         <f>'Nach Mannschaften sortiert'!H69</f>
         <v>Heim</v>
@@ -8608,6 +8638,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F79)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F79" s="82" t="s">
+        <v>205</v>
+      </c>
       <c r="G79" t="str">
         <f>'Nach Mannschaften sortiert'!H79</f>
         <v>Heim</v>
@@ -8997,6 +9030,9 @@
       <c r="E89" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F89)</f>
         <v>STEINBRUNN</v>
+      </c>
+      <c r="F89" s="82" t="s">
+        <v>203</v>
       </c>
       <c r="G89" t="str">
         <f>'Nach Mannschaften sortiert'!H89</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81ACC682-A0AC-4FA5-A72E-C8176F6687A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6D52D3-CC6B-4A29-B93D-B2641BBFAB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6D52D3-CC6B-4A29-B93D-B2641BBFAB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A317AFE5-596B-46DC-9C30-210F7C6A248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="212">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -667,6 +667,21 @@
   </si>
   <si>
     <t>4:3 für Stotzing</t>
+  </si>
+  <si>
+    <t>5:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>3:3</t>
+  </si>
+  <si>
+    <t>4:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>2:9 für Neufeld</t>
+  </si>
+  <si>
+    <t>15:13 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -6592,6 +6607,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F27" s="82" t="s">
+        <v>209</v>
+      </c>
       <c r="G27" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
         <v>Heim</v>
@@ -7111,6 +7129,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F40" s="82" t="s">
+        <v>207</v>
+      </c>
       <c r="G40" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
         <v>Heim</v>
@@ -7501,6 +7522,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
         <v>GOLS</v>
       </c>
+      <c r="F50" s="82" t="s">
+        <v>210</v>
+      </c>
       <c r="G50" t="str">
         <f>'Nach Mannschaften sortiert'!H50</f>
         <v>Auswärts</v>
@@ -8287,6 +8311,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F70)</f>
         <v>KLINGENBACH</v>
       </c>
+      <c r="F70" s="82" t="s">
+        <v>208</v>
+      </c>
       <c r="G70" t="str">
         <f>'Nach Mannschaften sortiert'!H70</f>
         <v>Auswärts</v>
@@ -9073,6 +9100,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F90)</f>
         <v>HORNSTEIN</v>
       </c>
+      <c r="F90" s="82" t="s">
+        <v>208</v>
+      </c>
       <c r="G90" t="str">
         <f>'Nach Mannschaften sortiert'!H90</f>
         <v>Auswärts</v>
@@ -9618,6 +9648,9 @@
       <c r="E104" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F104)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F104" s="82" t="s">
+        <v>211</v>
       </c>
       <c r="G104" t="str">
         <f>'Nach Mannschaften sortiert'!H104</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A317AFE5-596B-46DC-9C30-210F7C6A248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0C9AD9-8168-47DF-A873-8C32C7616278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="213">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -682,6 +682,9 @@
   </si>
   <si>
     <t>15:13 für Neufeld</t>
+  </si>
+  <si>
+    <t>3:2 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -8707,6 +8710,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F80)</f>
         <v>ST. GEORGEN</v>
       </c>
+      <c r="F80" s="82" t="s">
+        <v>212</v>
+      </c>
       <c r="G80" t="str">
         <f>'Nach Mannschaften sortiert'!H80</f>
         <v>Auswärts</v>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0C9AD9-8168-47DF-A873-8C32C7616278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94378C61-ABF5-4374-A4E4-5122EAE2792B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="219">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -685,6 +685,24 @@
   </si>
   <si>
     <t>3:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>2:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>6:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>6:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>3:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>2:5 für Parndorf</t>
+  </si>
+  <si>
+    <t>8:2 für Wulkaprodersdorf</t>
   </si>
 </sst>
 </file>
@@ -6652,6 +6670,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
         <v>GATTENDORF</v>
       </c>
+      <c r="F28" s="82" t="s">
+        <v>213</v>
+      </c>
       <c r="G28" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
         <v>Auswärts</v>
@@ -7174,6 +7195,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
         <v>GATTENDORF</v>
       </c>
+      <c r="F41" s="82" t="s">
+        <v>214</v>
+      </c>
       <c r="G41" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
         <v>Auswärts</v>
@@ -7567,6 +7591,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F51" s="82" t="s">
+        <v>216</v>
+      </c>
       <c r="G51" t="str">
         <f>'Nach Mannschaften sortiert'!H51</f>
         <v>Heim</v>
@@ -7999,6 +8026,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F62" s="82" t="s">
+        <v>217</v>
+      </c>
       <c r="G62" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
         <v>Heim</v>
@@ -8752,6 +8782,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F81)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F81" s="82" t="s">
+        <v>215</v>
+      </c>
       <c r="G81" t="str">
         <f>'Nach Mannschaften sortiert'!H81</f>
         <v>Auswärts</v>
@@ -9147,6 +9180,9 @@
       <c r="E91" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F91)</f>
         <v>WULKAPRODERSDORF</v>
+      </c>
+      <c r="F91" s="82" t="s">
+        <v>218</v>
       </c>
       <c r="G91" t="str">
         <f>'Nach Mannschaften sortiert'!H91</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94378C61-ABF5-4374-A4E4-5122EAE2792B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDC8E23-40D4-440D-848E-3F999D1F2A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="221">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -703,6 +703,12 @@
   </si>
   <si>
     <t>8:2 für Wulkaprodersdorf</t>
+  </si>
+  <si>
+    <t>5:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>0:0</t>
   </si>
 </sst>
 </file>
@@ -7987,6 +7993,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
         <v>NEUDÖRFL</v>
       </c>
+      <c r="F61" s="82" t="s">
+        <v>220</v>
+      </c>
       <c r="G61" t="str">
         <f>'Nach Mannschaften sortiert'!H61</f>
         <v>Auswärts</v>
@@ -8385,6 +8394,9 @@
       <c r="E71" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F71)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F71" s="82" t="s">
+        <v>219</v>
       </c>
       <c r="G71" t="str">
         <f>'Nach Mannschaften sortiert'!H71</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDC8E23-40D4-440D-848E-3F999D1F2A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73CF1AC-3301-4B35-AD27-2D4998018ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="224">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -709,6 +709,15 @@
   </si>
   <si>
     <t>0:0</t>
+  </si>
+  <si>
+    <t>9:4 für Neufeld</t>
+  </si>
+  <si>
+    <t>10:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>5:4 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -3719,7 +3728,7 @@
         <v>0.5</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>184</v>
@@ -5573,7 +5582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="82" customWidth="1"/>
@@ -8435,7 +8444,10 @@
       </c>
       <c r="E72" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F72)</f>
-        <v>RUST</v>
+        <v>EISENSTADT</v>
+      </c>
+      <c r="F72" s="82" t="s">
+        <v>223</v>
       </c>
       <c r="G72" t="str">
         <f>'Nach Mannschaften sortiert'!H72</f>
@@ -9664,6 +9676,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F103)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F103" s="82" t="s">
+        <v>221</v>
+      </c>
       <c r="G103" t="str">
         <f>'Nach Mannschaften sortiert'!H103</f>
         <v>Auswärts</v>
@@ -9784,6 +9799,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F106)</f>
         <v>EISENSTADT</v>
       </c>
+      <c r="F106" s="82" t="s">
+        <v>222</v>
+      </c>
       <c r="G106" t="str">
         <f>'Nach Mannschaften sortiert'!H106</f>
         <v>Auswärts</v>
@@ -10791,7 +10809,7 @@
         <v>0.375</v>
       </c>
       <c r="D132" s="94">
-        <f t="shared" ref="D132:D142" si="3">IF(I132="KM",C132+"1:45",IF(I132="U23",C132+"1:45",IF(I132="U16",C132+"1:45",IF(I132="U15",C132+"1:30",IF(I132="U14",C132+"1:30",IF(I132="U13",C132+"1:35",IF(I132="U12_1",C132+"1:10",IF(I132="U12_2",C132+"1:10",IF(I132="U11",C132+"1:10",IF(I132="U10",C132+"1:03",IF(I132="U9",C132+"1:03",C132+"3:00")))))))))))</f>
+        <f t="shared" ref="D132:D141" si="3">IF(I132="KM",C132+"1:45",IF(I132="U23",C132+"1:45",IF(I132="U16",C132+"1:45",IF(I132="U15",C132+"1:30",IF(I132="U14",C132+"1:30",IF(I132="U13",C132+"1:35",IF(I132="U12_1",C132+"1:10",IF(I132="U12_2",C132+"1:10",IF(I132="U11",C132+"1:10",IF(I132="U10",C132+"1:03",IF(I132="U9",C132+"1:03",C132+"3:00")))))))))))</f>
         <v>0.5</v>
       </c>
       <c r="E132" s="94" t="str">
@@ -11168,45 +11186,6 @@
         <v>80</v>
       </c>
       <c r="L141" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B142" s="93">
-        <f>'Nach Mannschaften sortiert'!D142</f>
-        <v>46291</v>
-      </c>
-      <c r="C142" s="94">
-        <f>'Nach Mannschaften sortiert'!E142</f>
-        <v>0.75</v>
-      </c>
-      <c r="D142" s="94">
-        <f t="shared" si="3"/>
-        <v>0.875</v>
-      </c>
-      <c r="E142" s="94" t="str">
-        <f>UPPER('Nach Mannschaften sortiert'!F142)</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="G142" t="str">
-        <f>'Nach Mannschaften sortiert'!H142</f>
-        <v>Heim</v>
-      </c>
-      <c r="H142" t="str">
-        <f>'Nach Mannschaften sortiert'!G142</f>
-        <v>Oktoberfest 2026</v>
-      </c>
-      <c r="I142" t="str">
-        <f>'Nach Mannschaften sortiert'!C142</f>
-        <v>Fest ASV Neufeld</v>
-      </c>
-      <c r="J142" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="K142" t="s">
-        <v>80</v>
-      </c>
-      <c r="L142" t="s">
         <v>79</v>
       </c>
     </row>
@@ -13845,7 +13824,7 @@
       </c>
       <c r="D58" s="57" t="str">
         <f>'ICS2'!E72</f>
-        <v>RUST</v>
+        <v>EISENSTADT</v>
       </c>
       <c r="E58" s="57" t="str">
         <f>'ICS2'!H72</f>
@@ -14245,43 +14224,43 @@
       </c>
     </row>
     <row r="67" spans="1:11" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="57" t="str">
-        <f>'ICS2'!I142</f>
-        <v>Fest ASV Neufeld</v>
-      </c>
-      <c r="B67" s="103">
-        <f>'ICS2'!B142</f>
-        <v>46291</v>
-      </c>
-      <c r="C67" s="104">
-        <f>'ICS2'!C142</f>
-        <v>0.75</v>
-      </c>
-      <c r="D67" s="57" t="str">
-        <f>'ICS2'!E142</f>
-        <v>NEUFELD</v>
-      </c>
-      <c r="E67" s="57" t="str">
-        <f>'ICS2'!H142</f>
-        <v>Oktoberfest 2026</v>
-      </c>
-      <c r="F67" s="57" t="str">
+      <c r="A67" s="57" t="e">
+        <f>'ICS2'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B67" s="103" t="e">
+        <f>'ICS2'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C67" s="104" t="e">
+        <f>'ICS2'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D67" s="57" t="e">
+        <f>'ICS2'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E67" s="57" t="e">
+        <f>'ICS2'!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F67" s="57" t="e">
         <f t="shared" si="15"/>
-        <v>Fest ASV Neufeld</v>
+        <v>#REF!</v>
       </c>
       <c r="G67" s="57"/>
       <c r="H67" s="57"/>
-      <c r="I67" s="57" t="str">
+      <c r="I67" s="57" t="e">
         <f>IF(F67="Großfeld","5",IF(F67="U16","5",IF(F67="U15","5",IF(F67="U14","4",IF(F67="U13","4",IF(F67="U11/U12","4",IF(F67="U9/U10","4",IF(F67="U9","4","3"))))))))</f>
-        <v>3</v>
-      </c>
-      <c r="J67" s="57" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="J67" s="57" t="e">
         <f t="shared" si="16"/>
-        <v>FEHLER</v>
-      </c>
-      <c r="K67" s="57" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="K67" s="57" t="e">
         <f t="shared" si="17"/>
-        <v>FEHLER</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="123" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
@@ -20050,7 +20029,7 @@
       </c>
       <c r="F49" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F72</f>
-        <v>Rust</v>
+        <v>Eisenstadt</v>
       </c>
       <c r="G49" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!G72</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73CF1AC-3301-4B35-AD27-2D4998018ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B36FE3-A54B-4EF5-9CFA-A6D20093AC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="230">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -718,6 +718,24 @@
   </si>
   <si>
     <t>5:4 für Neufeld</t>
+  </si>
+  <si>
+    <t>1:1</t>
+  </si>
+  <si>
+    <t>1:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>1:3 für Seewinkel</t>
+  </si>
+  <si>
+    <t>5:6 für Wulkaprodersdorf</t>
+  </si>
+  <si>
+    <t>8:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>2:2</t>
   </si>
 </sst>
 </file>
@@ -6727,6 +6745,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F29" s="82" t="s">
+        <v>224</v>
+      </c>
       <c r="G29" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
         <v>Heim</v>
@@ -7252,6 +7273,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F42" s="82" t="s">
+        <v>225</v>
+      </c>
       <c r="G42" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
         <v>Heim</v>
@@ -7648,6 +7672,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F52" s="82" t="s">
+        <v>229</v>
+      </c>
       <c r="G52" t="str">
         <f>'Nach Mannschaften sortiert'!H52</f>
         <v>Auswärts</v>
@@ -8086,6 +8113,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F63" s="82" t="s">
+        <v>226</v>
+      </c>
       <c r="G63" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>
         <v>Heim</v>
@@ -8848,6 +8878,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F82)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F82" s="82" t="s">
+        <v>228</v>
+      </c>
       <c r="G82" t="str">
         <f>'Nach Mannschaften sortiert'!H82</f>
         <v>Heim</v>
@@ -9246,6 +9279,9 @@
       <c r="E92" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F92)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F92" s="82" t="s">
+        <v>227</v>
       </c>
       <c r="G92" t="str">
         <f>'Nach Mannschaften sortiert'!H92</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B36FE3-A54B-4EF5-9CFA-A6D20093AC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814040D3-D333-4107-9B77-2A52F5623792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3767,10 +3767,10 @@
         <v>46</v>
       </c>
       <c r="D73" s="23">
-        <v>46298</v>
+        <v>46307</v>
       </c>
       <c r="E73" s="7">
-        <v>0.5</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>59</v>
@@ -8504,15 +8504,15 @@
     <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="93">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46298</v>
+        <v>46307</v>
       </c>
       <c r="C73" s="94">
         <f>'Nach Mannschaften sortiert'!E73</f>
-        <v>0.5</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D73" s="94">
         <f t="shared" si="2"/>
-        <v>0.54861111111111116</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E73" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F73)</f>
@@ -14813,11 +14813,11 @@
       </c>
       <c r="B79" s="118">
         <f>'ICS2'!B73</f>
-        <v>46298</v>
+        <v>46307</v>
       </c>
       <c r="C79" s="119">
         <f>'ICS2'!C73</f>
-        <v>0.5</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D79" s="117" t="str">
         <f>'ICS2'!E73</f>
@@ -20091,11 +20091,11 @@
       </c>
       <c r="D50" s="55">
         <f>'Nach Mannschaften sortiert'!D73</f>
-        <v>46298</v>
+        <v>46307</v>
       </c>
       <c r="E50" s="95">
         <f>'Nach Mannschaften sortiert'!E73</f>
-        <v>0.5</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F50" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F73</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814040D3-D333-4107-9B77-2A52F5623792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0686885-7604-4C99-9593-EF41D4A1BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="232">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -736,6 +736,12 @@
   </si>
   <si>
     <t>2:2</t>
+  </si>
+  <si>
+    <t>2:0 für Siegendorf</t>
+  </si>
+  <si>
+    <t>2:1 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -2690,10 +2696,10 @@
         <v>13</v>
       </c>
       <c r="D33" s="10">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="E33" s="3">
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>23</v>
@@ -3041,10 +3047,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="10">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="E46" s="3">
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>23</v>
@@ -6787,6 +6793,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
         <v>SIEGENDORF</v>
       </c>
+      <c r="F30" s="82" t="s">
+        <v>230</v>
+      </c>
       <c r="G30" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
         <v>Auswärts</v>
@@ -6890,15 +6899,15 @@
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="93">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="C33" s="94">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D33" s="94">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.88541666666666663</v>
       </c>
       <c r="E33" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
@@ -7315,6 +7324,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
         <v>SIEGENDORF</v>
       </c>
+      <c r="F43" s="82" t="s">
+        <v>229</v>
+      </c>
       <c r="G43" t="str">
         <f>'Nach Mannschaften sortiert'!H43</f>
         <v>Auswärts</v>
@@ -7418,15 +7430,15 @@
     <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="93">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="C46" s="94">
         <f>'Nach Mannschaften sortiert'!E46</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D46" s="94">
         <f t="shared" si="0"/>
-        <v>0.69791666666666663</v>
+        <v>0.80208333333333326</v>
       </c>
       <c r="E46" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
@@ -8919,6 +8931,9 @@
       <c r="E83" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
         <v>OGGAU</v>
+      </c>
+      <c r="F83" s="82" t="s">
+        <v>231</v>
       </c>
       <c r="G83" t="str">
         <f>'Nach Mannschaften sortiert'!H83</f>
@@ -15918,11 +15933,11 @@
       </c>
       <c r="B103" s="121">
         <f>'ICS2'!B46</f>
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="C103" s="122">
         <f>'ICS2'!C46</f>
-        <v>0.625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D103" s="120" t="str">
         <f>'ICS2'!E46</f>
@@ -16010,11 +16025,11 @@
       </c>
       <c r="B105" s="121">
         <f>'ICS2'!B33</f>
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="C105" s="122">
         <f>'ICS2'!C33</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="D105" s="120" t="str">
         <f>'ICS2'!E33</f>
@@ -18799,11 +18814,11 @@
       </c>
       <c r="D12" s="55">
         <f>'Nach Mannschaften sortiert'!D33</f>
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="E12" s="95">
         <f>'Nach Mannschaften sortiert'!E33</f>
-        <v>0.70833333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F12" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F33</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0686885-7604-4C99-9593-EF41D4A1BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED386B4-3D21-4C6C-867E-A3AECE34CFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -1809,7 +1809,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="54" bestFit="1" customWidth="1"/>
@@ -3389,7 +3389,7 @@
         <v>46340</v>
       </c>
       <c r="E59" s="22">
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="F59" s="21" t="s">
         <v>23</v>
@@ -4989,9 +4989,7 @@
       <c r="B119" s="42">
         <v>2</v>
       </c>
-      <c r="C119" s="42" t="s">
-        <v>53</v>
-      </c>
+      <c r="C119" s="42"/>
       <c r="D119" s="43"/>
       <c r="E119" s="44"/>
       <c r="F119" s="42"/>
@@ -5057,8 +5055,8 @@
       <c r="B123" s="30">
         <v>1</v>
       </c>
-      <c r="C123" s="30" t="s">
-        <v>54</v>
+      <c r="C123" s="42" t="s">
+        <v>53</v>
       </c>
       <c r="D123" s="58">
         <v>46230</v>
@@ -5354,8 +5352,8 @@
       <c r="B134" s="40">
         <v>2</v>
       </c>
-      <c r="C134" s="40" t="s">
-        <v>161</v>
+      <c r="C134" s="30" t="s">
+        <v>54</v>
       </c>
       <c r="D134" s="59">
         <v>46256</v>
@@ -5381,7 +5379,7 @@
       <c r="B135" s="54">
         <v>1</v>
       </c>
-      <c r="C135" s="54" t="s">
+      <c r="C135" s="40" t="s">
         <v>161</v>
       </c>
       <c r="D135" s="55">
@@ -5463,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="C138" s="54" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="D138" s="55">
         <v>46359</v>
@@ -5490,7 +5488,7 @@
         <v>4</v>
       </c>
       <c r="C139" s="54" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="D139" s="55">
         <v>46402</v>
@@ -5571,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="C142" s="54" t="s">
-        <v>63</v>
+        <v>161</v>
       </c>
       <c r="D142" s="55">
         <v>46291</v>
@@ -5587,6 +5585,11 @@
       </c>
       <c r="H142" s="54" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C143" s="54" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -7950,11 +7953,11 @@
       </c>
       <c r="C59" s="94">
         <f>'Nach Mannschaften sortiert'!E59</f>
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="D59" s="94">
         <f t="shared" si="0"/>
-        <v>0.53125</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E59" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F59)</f>
@@ -10369,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="str">
-        <f>'Nach Mannschaften sortiert'!C119</f>
+        <f>'Nach Mannschaften sortiert'!C120</f>
         <v>U7</v>
       </c>
       <c r="J119" s="82" t="s">
@@ -10408,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="str">
-        <f>'Nach Mannschaften sortiert'!C120</f>
+        <f>'Nach Mannschaften sortiert'!C121</f>
         <v>U7</v>
       </c>
       <c r="J120" s="82" t="s">
@@ -10447,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="str">
-        <f>'Nach Mannschaften sortiert'!C121</f>
+        <f>'Nach Mannschaften sortiert'!C122</f>
         <v>U7</v>
       </c>
       <c r="J121" s="82" t="s">
@@ -10486,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="str">
-        <f>'Nach Mannschaften sortiert'!C122</f>
+        <f>'Nach Mannschaften sortiert'!C123</f>
         <v>U7</v>
       </c>
       <c r="J122" s="82" t="s">
@@ -10525,7 +10528,7 @@
         <v>REAL MADRID CAMP</v>
       </c>
       <c r="I123" t="str">
-        <f>'Nach Mannschaften sortiert'!C123</f>
+        <f>'Nach Mannschaften sortiert'!C124</f>
         <v>Camp</v>
       </c>
       <c r="J123" s="82" t="s">
@@ -10564,7 +10567,7 @@
         <v>REAL MADRID CAMP</v>
       </c>
       <c r="I124" t="str">
-        <f>'Nach Mannschaften sortiert'!C124</f>
+        <f>'Nach Mannschaften sortiert'!C125</f>
         <v>Camp</v>
       </c>
       <c r="J124" s="82" t="s">
@@ -10603,7 +10606,7 @@
         <v>REAL MADRID CAMP</v>
       </c>
       <c r="I125" t="str">
-        <f>'Nach Mannschaften sortiert'!C125</f>
+        <f>'Nach Mannschaften sortiert'!C126</f>
         <v>Camp</v>
       </c>
       <c r="J125" s="82" t="s">
@@ -10642,7 +10645,7 @@
         <v>REAL MADRID CAMP</v>
       </c>
       <c r="I126" t="str">
-        <f>'Nach Mannschaften sortiert'!C126</f>
+        <f>'Nach Mannschaften sortiert'!C127</f>
         <v>Camp</v>
       </c>
       <c r="J126" s="82" t="s">
@@ -10681,7 +10684,7 @@
         <v>REAL MADRID CAMP</v>
       </c>
       <c r="I127" t="str">
-        <f>'Nach Mannschaften sortiert'!C127</f>
+        <f>'Nach Mannschaften sortiert'!C128</f>
         <v>Camp</v>
       </c>
       <c r="J127" s="82" t="s">
@@ -10720,7 +10723,7 @@
         <v>MÄDCHENCAMP</v>
       </c>
       <c r="I128" t="str">
-        <f>'Nach Mannschaften sortiert'!C128</f>
+        <f>'Nach Mannschaften sortiert'!C129</f>
         <v>Camp</v>
       </c>
       <c r="J128" s="82" t="s">
@@ -10759,7 +10762,7 @@
         <v>MÄDCHENCAMP</v>
       </c>
       <c r="I129" t="str">
-        <f>'Nach Mannschaften sortiert'!C129</f>
+        <f>'Nach Mannschaften sortiert'!C130</f>
         <v>Camp</v>
       </c>
       <c r="J129" s="82" t="s">
@@ -10798,7 +10801,7 @@
         <v>MÄDCHENCAMP</v>
       </c>
       <c r="I130" t="str">
-        <f>'Nach Mannschaften sortiert'!C130</f>
+        <f>'Nach Mannschaften sortiert'!C131</f>
         <v>Camp</v>
       </c>
       <c r="J130" s="82" t="s">
@@ -10837,7 +10840,7 @@
         <v>Teco 7 Camp</v>
       </c>
       <c r="I131" t="str">
-        <f>'Nach Mannschaften sortiert'!C131</f>
+        <f>'Nach Mannschaften sortiert'!C132</f>
         <v>Camp</v>
       </c>
       <c r="J131" s="82" t="s">
@@ -10876,7 +10879,7 @@
         <v>Teco 7 Camp</v>
       </c>
       <c r="I132" t="str">
-        <f>'Nach Mannschaften sortiert'!C132</f>
+        <f>'Nach Mannschaften sortiert'!C133</f>
         <v>Camp</v>
       </c>
       <c r="J132" s="82" t="s">
@@ -10915,7 +10918,7 @@
         <v>Teco 7 Camp</v>
       </c>
       <c r="I133" t="str">
-        <f>'Nach Mannschaften sortiert'!C133</f>
+        <f>'Nach Mannschaften sortiert'!C134</f>
         <v>Camp</v>
       </c>
       <c r="J133" s="82" t="s">
@@ -10954,7 +10957,7 @@
         <v>viele Gegner</v>
       </c>
       <c r="I134" t="str">
-        <f>'Nach Mannschaften sortiert'!C134</f>
+        <f>'Nach Mannschaften sortiert'!C135</f>
         <v>Turnier</v>
       </c>
       <c r="J134" s="82" t="s">
@@ -10993,7 +10996,7 @@
         <v>Hallencup 2026_27</v>
       </c>
       <c r="I135" t="str">
-        <f>'Nach Mannschaften sortiert'!C135</f>
+        <f>'Nach Mannschaften sortiert'!C136</f>
         <v>Turnier</v>
       </c>
       <c r="J135" s="82" t="s">
@@ -11032,7 +11035,7 @@
         <v>Hallencup 2026_27</v>
       </c>
       <c r="I136" t="str">
-        <f>'Nach Mannschaften sortiert'!C136</f>
+        <f>'Nach Mannschaften sortiert'!C137</f>
         <v>Turnier</v>
       </c>
       <c r="J136" s="82" t="s">
@@ -11071,7 +11074,7 @@
         <v>Hallencup 2026_27</v>
       </c>
       <c r="I137" t="str">
-        <f>'Nach Mannschaften sortiert'!C137</f>
+        <f>'Nach Mannschaften sortiert'!C138</f>
         <v>Turnier</v>
       </c>
       <c r="J137" s="82" t="s">
@@ -11110,7 +11113,7 @@
         <v>Weihnachtsfeier 2026</v>
       </c>
       <c r="I138" t="str">
-        <f>'Nach Mannschaften sortiert'!C138</f>
+        <f>'Nach Mannschaften sortiert'!C139</f>
         <v>Weihnachtsfeier</v>
       </c>
       <c r="J138" s="82" t="s">
@@ -11149,7 +11152,7 @@
         <v>Hallencup 2026_27</v>
       </c>
       <c r="I139" t="str">
-        <f>'Nach Mannschaften sortiert'!C139</f>
+        <f>'Nach Mannschaften sortiert'!C140</f>
         <v>Turnier</v>
       </c>
       <c r="J139" s="82" t="s">
@@ -11188,7 +11191,7 @@
         <v>Hallencup 2026_27</v>
       </c>
       <c r="I140" t="str">
-        <f>'Nach Mannschaften sortiert'!C140</f>
+        <f>'Nach Mannschaften sortiert'!C141</f>
         <v>Turnier</v>
       </c>
       <c r="J140" s="82" t="s">
@@ -11227,7 +11230,7 @@
         <v>Hallencup 2026_27</v>
       </c>
       <c r="I141" t="str">
-        <f>'Nach Mannschaften sortiert'!C141</f>
+        <f>'Nach Mannschaften sortiert'!C142</f>
         <v>Turnier</v>
       </c>
       <c r="J141" s="82" t="s">
@@ -17205,7 +17208,7 @@
       </c>
       <c r="C131" s="122">
         <f>'ICS2'!C59</f>
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="D131" s="120" t="str">
         <f>'ICS2'!E59</f>
@@ -18707,7 +18710,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C123</f>
+        <f>'Nach Mannschaften sortiert'!C124</f>
         <v>Camp</v>
       </c>
       <c r="D9" s="53">
@@ -18775,7 +18778,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C124</f>
+        <f>'Nach Mannschaften sortiert'!C125</f>
         <v>Camp</v>
       </c>
       <c r="D11" s="53">
@@ -18877,7 +18880,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="52" t="str">
-        <f>'Nach Mannschaften sortiert'!C125</f>
+        <f>'Nach Mannschaften sortiert'!C126</f>
         <v>Camp</v>
       </c>
       <c r="D14" s="53">
@@ -20983,7 +20986,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C119</f>
+        <f>'Nach Mannschaften sortiert'!C120</f>
         <v>U7</v>
       </c>
       <c r="D76" s="55">
@@ -21017,7 +21020,7 @@
         <v>3</v>
       </c>
       <c r="C77" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C120</f>
+        <f>'Nach Mannschaften sortiert'!C121</f>
         <v>U7</v>
       </c>
       <c r="D77" s="55">
@@ -21051,7 +21054,7 @@
         <v>4</v>
       </c>
       <c r="C78" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C121</f>
+        <f>'Nach Mannschaften sortiert'!C122</f>
         <v>U7</v>
       </c>
       <c r="D78" s="55">
@@ -21085,7 +21088,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C122</f>
+        <f>'Nach Mannschaften sortiert'!C123</f>
         <v>U7</v>
       </c>
       <c r="D79" s="55">
@@ -21255,7 +21258,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="54" t="str">
-        <f>'Nach Mannschaften sortiert'!C134</f>
+        <f>'Nach Mannschaften sortiert'!C135</f>
         <v>Turnier</v>
       </c>
       <c r="D84" s="55">

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED386B4-3D21-4C6C-867E-A3AECE34CFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475F33AC-802F-4EE6-A05E-02C47EC4D9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="234">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -742,6 +742,12 @@
   </si>
   <si>
     <t>2:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>5:6 für Hornstein</t>
+  </si>
+  <si>
+    <t>11:6 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -9340,6 +9346,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F93)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F93" s="82" t="s">
+        <v>232</v>
+      </c>
       <c r="G93" t="str">
         <f>'Nach Mannschaften sortiert'!H93</f>
         <v>Heim</v>
@@ -9894,6 +9903,9 @@
       <c r="E107" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F107)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F107" s="82" t="s">
+        <v>233</v>
       </c>
       <c r="G107" t="str">
         <f>'Nach Mannschaften sortiert'!H107</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475F33AC-802F-4EE6-A05E-02C47EC4D9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF1260C-DBA0-4170-B400-7300FFD2AF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="235">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -748,6 +748,9 @@
   </si>
   <si>
     <t>11:6 für Neufeld</t>
+  </si>
+  <si>
+    <t>7:0 für Draßburg</t>
   </si>
 </sst>
 </file>
@@ -7735,6 +7738,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F53" s="82" t="s">
+        <v>216</v>
+      </c>
       <c r="G53" t="str">
         <f>'Nach Mannschaften sortiert'!H53</f>
         <v>Heim</v>
@@ -8175,6 +8181,9 @@
       <c r="E64" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F64)</f>
         <v>DRAßBURG</v>
+      </c>
+      <c r="F64" s="82" t="s">
+        <v>234</v>
       </c>
       <c r="G64" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF1260C-DBA0-4170-B400-7300FFD2AF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542D3CEC-C64C-4968-BD92-35079FB54B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="239">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -751,6 +751,18 @@
   </si>
   <si>
     <t>7:0 für Draßburg</t>
+  </si>
+  <si>
+    <t>3:1 für Wimpassing</t>
+  </si>
+  <si>
+    <t>7:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>16:2 für Leithaprodersdorf</t>
+  </si>
+  <si>
+    <t>11:2 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -6847,6 +6859,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F31" s="82" t="s">
+        <v>225</v>
+      </c>
       <c r="G31" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
         <v>Heim</v>
@@ -7378,6 +7393,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F44)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F44" s="82" t="s">
+        <v>235</v>
+      </c>
       <c r="G44" t="str">
         <f>'Nach Mannschaften sortiert'!H44</f>
         <v>Heim</v>
@@ -7780,6 +7798,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F54" s="82" t="s">
+        <v>224</v>
+      </c>
       <c r="G54" t="str">
         <f>'Nach Mannschaften sortiert'!H54</f>
         <v>Heim</v>
@@ -8587,6 +8608,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F74)</f>
         <v>STOTZING</v>
       </c>
+      <c r="F74" s="82" t="s">
+        <v>209</v>
+      </c>
       <c r="G74" t="str">
         <f>'Nach Mannschaften sortiert'!H74</f>
         <v>Auswärts</v>
@@ -8992,6 +9016,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
         <v>ST. MARGARETHEN</v>
       </c>
+      <c r="F84" s="82" t="s">
+        <v>236</v>
+      </c>
       <c r="G84" t="str">
         <f>'Nach Mannschaften sortiert'!H84</f>
         <v>Auswärts</v>
@@ -9397,6 +9424,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F94)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
+      <c r="F94" s="82" t="s">
+        <v>237</v>
+      </c>
       <c r="G94" t="str">
         <f>'Nach Mannschaften sortiert'!H94</f>
         <v>Auswärts</v>
@@ -9954,6 +9984,9 @@
       <c r="E108" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F108)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F108" s="82" t="s">
+        <v>238</v>
       </c>
       <c r="G108" t="str">
         <f>'Nach Mannschaften sortiert'!H108</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542D3CEC-C64C-4968-BD92-35079FB54B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AECB8F9-85FC-4BBE-B4E7-DCDD446395A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="240">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -684,18 +684,12 @@
     <t>15:13 für Neufeld</t>
   </si>
   <si>
-    <t>3:2 für Neufeld</t>
-  </si>
-  <si>
     <t>2:0 für Neufeld</t>
   </si>
   <si>
     <t>6:1 für Neufeld</t>
   </si>
   <si>
-    <t>6:2 für Neufeld</t>
-  </si>
-  <si>
     <t>3:0 für Neufeld</t>
   </si>
   <si>
@@ -705,9 +699,6 @@
     <t>8:2 für Wulkaprodersdorf</t>
   </si>
   <si>
-    <t>5:2 für Neufeld</t>
-  </si>
-  <si>
     <t>0:0</t>
   </si>
   <si>
@@ -717,9 +708,6 @@
     <t>10:1 für Neufeld</t>
   </si>
   <si>
-    <t>5:4 für Neufeld</t>
-  </si>
-  <si>
     <t>1:1</t>
   </si>
   <si>
@@ -732,18 +720,12 @@
     <t>5:6 für Wulkaprodersdorf</t>
   </si>
   <si>
-    <t>8:1 für Neufeld</t>
-  </si>
-  <si>
     <t>2:2</t>
   </si>
   <si>
     <t>2:0 für Siegendorf</t>
   </si>
   <si>
-    <t>2:1 für Neufeld</t>
-  </si>
-  <si>
     <t>5:6 für Hornstein</t>
   </si>
   <si>
@@ -756,13 +738,34 @@
     <t>3:1 für Wimpassing</t>
   </si>
   <si>
-    <t>7:2 für Neufeld</t>
-  </si>
-  <si>
     <t>16:2 für Leithaprodersdorf</t>
   </si>
   <si>
     <t>11:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>3:2 für SPG ASV</t>
+  </si>
+  <si>
+    <t>6:2 für SPG ASV</t>
+  </si>
+  <si>
+    <t>8:1 für SPG ASV</t>
+  </si>
+  <si>
+    <t>2:1 für SPG ASV</t>
+  </si>
+  <si>
+    <t>7:2 für SPG ASV</t>
+  </si>
+  <si>
+    <t>5:2 für SPG ASV</t>
+  </si>
+  <si>
+    <t>5:4 für SPG ASV</t>
+  </si>
+  <si>
+    <t>4:0 für SPG ASV</t>
   </si>
 </sst>
 </file>
@@ -4118,10 +4121,10 @@
         <v>47</v>
       </c>
       <c r="D85" s="89">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="E85" s="90">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="F85" s="88" t="s">
         <v>23</v>
@@ -6734,7 +6737,7 @@
         <v>GATTENDORF</v>
       </c>
       <c r="F28" s="82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G28" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
@@ -6776,7 +6779,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F29" s="82" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G29" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
@@ -6818,7 +6821,7 @@
         <v>SIEGENDORF</v>
       </c>
       <c r="F30" s="82" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G30" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
@@ -6860,7 +6863,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F31" s="82" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G31" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
@@ -7268,7 +7271,7 @@
         <v>GATTENDORF</v>
       </c>
       <c r="F41" s="82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G41" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
@@ -7310,7 +7313,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F42" s="82" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G42" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
@@ -7352,7 +7355,7 @@
         <v>SIEGENDORF</v>
       </c>
       <c r="F43" s="82" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G43" t="str">
         <f>'Nach Mannschaften sortiert'!H43</f>
@@ -7394,7 +7397,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F44" s="82" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G44" t="str">
         <f>'Nach Mannschaften sortiert'!H44</f>
@@ -7673,7 +7676,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F51" s="82" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G51" t="str">
         <f>'Nach Mannschaften sortiert'!H51</f>
@@ -7715,7 +7718,7 @@
         <v>GROßHÖFLEIN</v>
       </c>
       <c r="F52" s="82" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G52" t="str">
         <f>'Nach Mannschaften sortiert'!H52</f>
@@ -7757,7 +7760,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F53" s="82" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G53" t="str">
         <f>'Nach Mannschaften sortiert'!H53</f>
@@ -7799,7 +7802,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F54" s="82" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G54" t="str">
         <f>'Nach Mannschaften sortiert'!H54</f>
@@ -8078,7 +8081,7 @@
         <v>NEUDÖRFL</v>
       </c>
       <c r="F61" s="82" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G61" t="str">
         <f>'Nach Mannschaften sortiert'!H61</f>
@@ -8120,7 +8123,7 @@
         <v>GROßHÖFLEIN</v>
       </c>
       <c r="F62" s="82" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G62" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
@@ -8162,7 +8165,7 @@
         <v>GROßHÖFLEIN</v>
       </c>
       <c r="F63" s="82" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G63" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>
@@ -8204,7 +8207,7 @@
         <v>DRAßBURG</v>
       </c>
       <c r="F64" s="82" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G64" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>
@@ -8486,7 +8489,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F71" s="82" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="G71" t="str">
         <f>'Nach Mannschaften sortiert'!H71</f>
@@ -8528,7 +8531,7 @@
         <v>EISENSTADT</v>
       </c>
       <c r="F72" s="82" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="G72" t="str">
         <f>'Nach Mannschaften sortiert'!H72</f>
@@ -8569,6 +8572,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F73)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F73" s="82" t="s">
+        <v>235</v>
+      </c>
       <c r="G73" t="str">
         <f>'Nach Mannschaften sortiert'!H73</f>
         <v>Heim</v>
@@ -8609,7 +8615,7 @@
         <v>STOTZING</v>
       </c>
       <c r="F74" s="82" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="G74" t="str">
         <f>'Nach Mannschaften sortiert'!H74</f>
@@ -8849,7 +8855,7 @@
         <v>ST. GEORGEN</v>
       </c>
       <c r="F80" s="82" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="G80" t="str">
         <f>'Nach Mannschaften sortiert'!H80</f>
@@ -8891,7 +8897,7 @@
         <v>GROßHÖFLEIN</v>
       </c>
       <c r="F81" s="82" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="G81" t="str">
         <f>'Nach Mannschaften sortiert'!H81</f>
@@ -8933,7 +8939,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F82" s="82" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="G82" t="str">
         <f>'Nach Mannschaften sortiert'!H82</f>
@@ -8975,7 +8981,7 @@
         <v>OGGAU</v>
       </c>
       <c r="F83" s="82" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G83" t="str">
         <f>'Nach Mannschaften sortiert'!H83</f>
@@ -9044,15 +9050,15 @@
     <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85" s="93">
         <f>'Nach Mannschaften sortiert'!D85</f>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="C85" s="94">
         <f>'Nach Mannschaften sortiert'!E85</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="D85" s="94">
         <f t="shared" si="2"/>
-        <v>0.67361111111111116</v>
+        <v>0.79861111111111116</v>
       </c>
       <c r="E85" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
@@ -9299,7 +9305,7 @@
         <v>WULKAPRODERSDORF</v>
       </c>
       <c r="F91" s="82" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G91" t="str">
         <f>'Nach Mannschaften sortiert'!H91</f>
@@ -9341,7 +9347,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F92" s="82" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G92" t="str">
         <f>'Nach Mannschaften sortiert'!H92</f>
@@ -9383,7 +9389,7 @@
         <v>STEINBRUNN</v>
       </c>
       <c r="F93" s="82" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G93" t="str">
         <f>'Nach Mannschaften sortiert'!H93</f>
@@ -9425,7 +9431,7 @@
         <v>LEITHAPRODERSDORF</v>
       </c>
       <c r="F94" s="82" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G94" t="str">
         <f>'Nach Mannschaften sortiert'!H94</f>
@@ -9779,7 +9785,7 @@
         <v>GROßHÖFLEIN</v>
       </c>
       <c r="F103" s="82" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G103" t="str">
         <f>'Nach Mannschaften sortiert'!H103</f>
@@ -9902,7 +9908,7 @@
         <v>EISENSTADT</v>
       </c>
       <c r="F106" s="82" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G106" t="str">
         <f>'Nach Mannschaften sortiert'!H106</f>
@@ -9944,7 +9950,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F107" s="82" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G107" t="str">
         <f>'Nach Mannschaften sortiert'!H107</f>
@@ -9986,7 +9992,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F108" s="82" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G108" t="str">
         <f>'Nach Mannschaften sortiert'!H108</f>
@@ -15806,11 +15812,11 @@
       </c>
       <c r="B99" s="121">
         <f>'ICS2'!B85</f>
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="C99" s="122">
         <f>'ICS2'!C85</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="D99" s="120" t="str">
         <f>'ICS2'!E85</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AECB8F9-85FC-4BBE-B4E7-DCDD446395A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C61804E-C6BF-4A9B-A141-1AFC5A26710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3854,7 +3854,7 @@
         <v>46312</v>
       </c>
       <c r="E75" s="7">
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>23</v>
@@ -8646,11 +8646,11 @@
       </c>
       <c r="C75" s="94">
         <f>'Nach Mannschaften sortiert'!E75</f>
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D75" s="94">
         <f t="shared" si="2"/>
-        <v>0.75694444444444453</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="E75" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="C100" s="122">
         <f>'ICS2'!C75</f>
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D100" s="120" t="str">
         <f>'ICS2'!E75</f>
@@ -20275,7 +20275,7 @@
       </c>
       <c r="E53" s="95">
         <f>'Nach Mannschaften sortiert'!E75</f>
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="F53" s="54" t="str">
         <f>'Nach Mannschaften sortiert'!F75</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C61804E-C6BF-4A9B-A141-1AFC5A26710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6373D6B-3683-4A91-9A42-929C3D1B77DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4127,7 +4127,7 @@
         <v>0.75</v>
       </c>
       <c r="F85" s="88" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="G85" s="88" t="s">
         <v>165</v>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="E85" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
-        <v>NEUFELD</v>
+        <v>STEINBRUNN</v>
       </c>
       <c r="G85" t="str">
         <f>'Nach Mannschaften sortiert'!H85</f>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="D99" s="120" t="str">
         <f>'ICS2'!E85</f>
-        <v>NEUFELD</v>
+        <v>STEINBRUNN</v>
       </c>
       <c r="E99" s="120" t="str">
         <f>'ICS2'!H85</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6373D6B-3683-4A91-9A42-929C3D1B77DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403AAE9A-0957-4205-90CD-A5C6FE366565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3905,13 +3905,13 @@
         <v>46</v>
       </c>
       <c r="D77" s="23">
-        <v>46326</v>
+        <v>46316</v>
       </c>
       <c r="E77" s="7">
-        <v>0.52083333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>184</v>
@@ -8720,19 +8720,19 @@
     <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77" s="93">
         <f>'Nach Mannschaften sortiert'!D77</f>
-        <v>46326</v>
+        <v>46316</v>
       </c>
       <c r="C77" s="94">
         <f>'Nach Mannschaften sortiert'!E77</f>
-        <v>0.52083333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D77" s="94">
         <f t="shared" si="2"/>
-        <v>0.56944444444444453</v>
+        <v>0.79861111111111116</v>
       </c>
       <c r="E77" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F77)</f>
-        <v>NEUFELD</v>
+        <v>STEINBRUNN</v>
       </c>
       <c r="G77" t="str">
         <f>'Nach Mannschaften sortiert'!H77</f>
@@ -16717,15 +16717,15 @@
       </c>
       <c r="B119" s="121">
         <f>'ICS2'!B77</f>
-        <v>46326</v>
+        <v>46316</v>
       </c>
       <c r="C119" s="122">
         <f>'ICS2'!C77</f>
-        <v>0.52083333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D119" s="120" t="str">
         <f>'ICS2'!E77</f>
-        <v>NEUFELD</v>
+        <v>STEINBRUNN</v>
       </c>
       <c r="E119" s="120" t="str">
         <f>'ICS2'!H77</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403AAE9A-0957-4205-90CD-A5C6FE366565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6402A07D-8CA7-4602-80F1-93B8C97A9B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="244">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -766,6 +766,18 @@
   </si>
   <si>
     <t>4:0 für SPG ASV</t>
+  </si>
+  <si>
+    <t>5:0 für Hornstein</t>
+  </si>
+  <si>
+    <t>3:1 für Hornstein</t>
+  </si>
+  <si>
+    <t>13:3  für St. Georgen</t>
+  </si>
+  <si>
+    <t>12:9 für Steinbrunn</t>
   </si>
 </sst>
 </file>
@@ -6904,6 +6916,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
         <v>HORNSTEIN</v>
       </c>
+      <c r="F32" s="82" t="s">
+        <v>240</v>
+      </c>
       <c r="G32" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
         <v>Auswärts</v>
@@ -7438,6 +7453,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F45)</f>
         <v>HORNSTEIN</v>
       </c>
+      <c r="F45" s="82" t="s">
+        <v>241</v>
+      </c>
       <c r="G45" t="str">
         <f>'Nach Mannschaften sortiert'!H45</f>
         <v>Auswärts</v>
@@ -7843,6 +7861,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F55)</f>
         <v>ST. GEORGEN</v>
       </c>
+      <c r="F55" s="82" t="s">
+        <v>214</v>
+      </c>
       <c r="G55" t="str">
         <f>'Nach Mannschaften sortiert'!H55</f>
         <v>Auswärts</v>
@@ -9064,6 +9085,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
         <v>STEINBRUNN</v>
       </c>
+      <c r="F85" s="82" t="s">
+        <v>242</v>
+      </c>
       <c r="G85" t="str">
         <f>'Nach Mannschaften sortiert'!H85</f>
         <v>Heim</v>
@@ -10032,6 +10056,9 @@
       <c r="E109" s="94" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F109)</f>
         <v>STEINBRUNN</v>
+      </c>
+      <c r="F109" s="82" t="s">
+        <v>243</v>
       </c>
       <c r="G109" t="str">
         <f>'Nach Mannschaften sortiert'!H109</f>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6402A07D-8CA7-4602-80F1-93B8C97A9B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36A51D8-C693-427D-B01B-4102D068EDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="245">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -778,6 +778,9 @@
   </si>
   <si>
     <t>12:9 für Steinbrunn</t>
+  </si>
+  <si>
+    <t>5:1 für Leithaprodersdorf</t>
   </si>
 </sst>
 </file>
@@ -9496,6 +9499,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F95)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F95" s="82" t="s">
+        <v>244</v>
+      </c>
       <c r="G95" t="str">
         <f>'Nach Mannschaften sortiert'!H95</f>
         <v>Heim</v>

--- a/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36A51D8-C693-427D-B01B-4102D068EDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FF009B-F925-4FA1-B464-4BCAEA131CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="246">
   <si>
     <t>fortlaufende Nummer</t>
   </si>
@@ -781,6 +781,9 @@
   </si>
   <si>
     <t>5:1 für Leithaprodersdorf</t>
+  </si>
+  <si>
+    <t>3:1 für SPG ASV</t>
   </si>
 </sst>
 </file>
@@ -8680,6 +8683,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F75" s="82" t="s">
+        <v>245</v>
+      </c>
       <c r="G75" t="str">
         <f>'Nach Mannschaften sortiert'!H75</f>
         <v>Heim</v>
